--- a/Assets/GameData/ObjectHeadData.xlsx
+++ b/Assets/GameData/ObjectHeadData.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="번역" sheetId="1" r:id="Re7601841e1364648"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수치" sheetId="2" r:id="R82cfeb404cdc4dae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계산기" sheetId="3" r:id="R212a26b4404d4be4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="번역" sheetId="1" r:id="Rc940989237ed4c19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수치" sheetId="2" r:id="R253d0154945f4121"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계산기" sheetId="3" r:id="R76a4586707144050"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0.###"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -49,6 +49,10 @@
     <x:font>
       <x:sz val="11"/>
       <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="맑은 고딕"/>
     </x:font>
   </x:fonts>
   <x:fills count="6">
@@ -193,7 +197,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="44">
+  <x:cellXfs count="46">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -292,6 +296,10 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -300,7 +308,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LocalizationTable" displayName="LocalizationTable" ref="A4:D56" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LocalizationTable" displayName="LocalizationTable" ref="A4:D125" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="key"/>
     <x:tableColumn id="2" name="한국어"/>
@@ -1291,6 +1299,986 @@
         <x:v>오류 상태</x:v>
       </x:c>
     </x:row>
+    <x:row r="57" ht="52" customHeight="1">
+      <x:c r="A57" s="45" t="str">
+        <x:v>selection_required</x:v>
+      </x:c>
+      <x:c r="B57" s="45" t="str">
+        <x:v>캐릭터 선택을 완료해 주세요.</x:v>
+      </x:c>
+      <x:c r="C57" s="45" t="str">
+        <x:v>Complete your character selection.</x:v>
+      </x:c>
+      <x:c r="D57" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="52" customHeight="1">
+      <x:c r="A58" s="45" t="str">
+        <x:v>your_team</x:v>
+      </x:c>
+      <x:c r="B58" s="45" t="str">
+        <x:v>내 팀 편성</x:v>
+      </x:c>
+      <x:c r="C58" s="45" t="str">
+        <x:v>YOUR SQUAD</x:v>
+      </x:c>
+      <x:c r="D58" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="52" customHeight="1">
+      <x:c r="A59" s="45" t="str">
+        <x:v>select_player_team</x:v>
+      </x:c>
+      <x:c r="B59" s="45" t="str">
+        <x:v>P{0} 팀을 선택하세요</x:v>
+      </x:c>
+      <x:c r="C59" s="45" t="str">
+        <x:v>SELECT P{0}'S SQUAD</x:v>
+      </x:c>
+      <x:c r="D59" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="52" customHeight="1">
+      <x:c r="A60" s="45" t="str">
+        <x:v>selection_hint</x:v>
+      </x:c>
+      <x:c r="B60" s="45" t="str">
+        <x:v>슬롯을 고르고 캐릭터를 선택하세요. {0}개 · 중복 선택 가능</x:v>
+      </x:c>
+      <x:c r="C60" s="45" t="str">
+        <x:v>Select a slot, then a character. {0} slots · duplicates allowed</x:v>
+      </x:c>
+      <x:c r="D60" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="52" customHeight="1">
+      <x:c r="A61" s="45" t="str">
+        <x:v>bulb_name</x:v>
+      </x:c>
+      <x:c r="B61" s="45" t="str">
+        <x:v>전구</x:v>
+      </x:c>
+      <x:c r="C61" s="45" t="str">
+        <x:v>BULB</x:v>
+      </x:c>
+      <x:c r="D61" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="52" customHeight="1">
+      <x:c r="A62" s="45" t="str">
+        <x:v>seed_name</x:v>
+      </x:c>
+      <x:c r="B62" s="45" t="str">
+        <x:v>씨앗</x:v>
+      </x:c>
+      <x:c r="C62" s="45" t="str">
+        <x:v>SEED</x:v>
+      </x:c>
+      <x:c r="D62" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="52" customHeight="1">
+      <x:c r="A63" s="45" t="str">
+        <x:v>bomb_name</x:v>
+      </x:c>
+      <x:c r="B63" s="45" t="str">
+        <x:v>폭탄</x:v>
+      </x:c>
+      <x:c r="C63" s="45" t="str">
+        <x:v>BOMB</x:v>
+      </x:c>
+      <x:c r="D63" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="52" customHeight="1">
+      <x:c r="A64" s="45" t="str">
+        <x:v>bulb_description</x:v>
+      </x:c>
+      <x:c r="B64" s="45" t="str">
+        <x:v>지역 통제형 · 유리 파편, 전기 장판, 연쇄 섬광으로 적의 움직임을 제한합니다.</x:v>
+      </x:c>
+      <x:c r="C64" s="45" t="str">
+        <x:v>CONTROL · Glass shards, electric fields and chain flashes restrict enemy movement.</x:v>
+      </x:c>
+      <x:c r="D64" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="52" customHeight="1">
+      <x:c r="A65" s="45" t="str">
+        <x:v>seed_description</x:v>
+      </x:c>
+      <x:c r="B65" s="45" t="str">
+        <x:v>지형 설계형 · 발판과 덩굴을 만들어 이동로를 열고 가시 장판으로 길목을 지킵니다.</x:v>
+      </x:c>
+      <x:c r="C65" s="45" t="str">
+        <x:v>TERRAIN · Create platforms and vines, open new routes and defend with thorns.</x:v>
+      </x:c>
+      <x:c r="D65" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="52" customHeight="1">
+      <x:c r="A66" s="45" t="str">
+        <x:v>bomb_description</x:v>
+      </x:c>
+      <x:c r="B66" s="45" t="str">
+        <x:v>파괴 공격형 · 기본 폭탄, 지연 폭탄과 집속탄으로 엄폐물을 무너뜨립니다.</x:v>
+      </x:c>
+      <x:c r="C66" s="45" t="str">
+        <x:v>DEMOLITION · Break cover with direct bombs, delayed blasts and cluster attacks.</x:v>
+      </x:c>
+      <x:c r="D66" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="52" customHeight="1">
+      <x:c r="A67" s="45" t="str">
+        <x:v>local_play</x:v>
+      </x:c>
+      <x:c r="B67" s="45" t="str">
+        <x:v>한 PC에서 플레이</x:v>
+      </x:c>
+      <x:c r="C67" s="45" t="str">
+        <x:v>PLAY ON ONE PC</x:v>
+      </x:c>
+      <x:c r="D67" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="52" customHeight="1">
+      <x:c r="A68" s="45" t="str">
+        <x:v>local_title</x:v>
+      </x:c>
+      <x:c r="B68" s="45" t="str">
+        <x:v>로컬 대전 · 팀 편성</x:v>
+      </x:c>
+      <x:c r="C68" s="45" t="str">
+        <x:v>LOCAL MATCH · SQUAD SELECT</x:v>
+      </x:c>
+      <x:c r="D68" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="52" customHeight="1">
+      <x:c r="A69" s="45" t="str">
+        <x:v>local_shared_screen</x:v>
+      </x:c>
+      <x:c r="B69" s="45" t="str">
+        <x:v>같은 화면에서 번갈아 플레이합니다</x:v>
+      </x:c>
+      <x:c r="C69" s="45" t="str">
+        <x:v>SHARED SCREEN · TAKE TURNS</x:v>
+      </x:c>
+      <x:c r="D69" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="52" customHeight="1">
+      <x:c r="A70" s="45" t="str">
+        <x:v>local_instructions</x:v>
+      </x:c>
+      <x:c r="B70" s="45" t="str">
+        <x:v>각 플레이어의 팀을 확정한 뒤 게임을 시작하세요.</x:v>
+      </x:c>
+      <x:c r="C70" s="45" t="str">
+        <x:v>Confirm each player's squad, then start the match.</x:v>
+      </x:c>
+      <x:c r="D70" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="52" customHeight="1">
+      <x:c r="A71" s="45" t="str">
+        <x:v>confirm_team</x:v>
+      </x:c>
+      <x:c r="B71" s="45" t="str">
+        <x:v>팀 확정 / 다음 플레이어</x:v>
+      </x:c>
+      <x:c r="C71" s="45" t="str">
+        <x:v>CONFIRM SQUAD / NEXT PLAYER</x:v>
+      </x:c>
+      <x:c r="D71" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="52" customHeight="1">
+      <x:c r="A72" s="45" t="str">
+        <x:v>saving_team</x:v>
+      </x:c>
+      <x:c r="B72" s="45" t="str">
+        <x:v>팀 선택을 동기화하는 중...</x:v>
+      </x:c>
+      <x:c r="C72" s="45" t="str">
+        <x:v>Synchronizing squad...</x:v>
+      </x:c>
+      <x:c r="D72" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="52" customHeight="1">
+      <x:c r="A73" s="45" t="str">
+        <x:v>help</x:v>
+      </x:c>
+      <x:c r="B73" s="45" t="str">
+        <x:v>플레이 방법</x:v>
+      </x:c>
+      <x:c r="C73" s="45" t="str">
+        <x:v>HOW TO PLAY</x:v>
+      </x:c>
+      <x:c r="D73" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="52" customHeight="1">
+      <x:c r="A74" s="45" t="str">
+        <x:v>close</x:v>
+      </x:c>
+      <x:c r="B74" s="45" t="str">
+        <x:v>닫기</x:v>
+      </x:c>
+      <x:c r="C74" s="45" t="str">
+        <x:v>CLOSE</x:v>
+      </x:c>
+      <x:c r="D74" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="52" customHeight="1">
+      <x:c r="A75" s="45" t="str">
+        <x:v>quit</x:v>
+      </x:c>
+      <x:c r="B75" s="45" t="str">
+        <x:v>게임 종료</x:v>
+      </x:c>
+      <x:c r="C75" s="45" t="str">
+        <x:v>QUIT GAME</x:v>
+      </x:c>
+      <x:c r="D75" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="52" customHeight="1">
+      <x:c r="A76" s="45" t="str">
+        <x:v>help_body</x:v>
+      </x:c>
+      <x:c r="B76" s="45" t="str">
+        <x:v>A / D : 이동   W : 점프
+마우스 : 조준   Space : 차징 / 발사
+C : 차징 취소   1 / 2 / 3 : 고유 스킬
+6 / 7 / 8 : 공용 머리   Esc : 선택 취소
+Tab : 턴 종료   휠 : 카메라 확대 / 축소
+공격 후에도 잔존 시간 동안 이동할 수 있습니다.
+마지막까지 살아남은 플레이어의 팀이 승리합니다.
+공용 머리는 같은 팀이 공유하는 일회성 아이템입니다.</x:v>
+      </x:c>
+      <x:c r="C76" s="45" t="str">
+        <x:v>A / D: move   W: jump
+Mouse: aim   Space: charge / fire
+C: cancel charge   1 / 2 / 3: skills
+6 / 7 / 8: common heads   Esc: cancel selection
+Tab: end turn   Wheel: zoom
+You can still move during residual time after attacking.
+The last surviving player's squad wins.
+Common heads are single-use items shared by your squad.</x:v>
+      </x:c>
+      <x:c r="D76" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="52" customHeight="1">
+      <x:c r="A77" s="45" t="str">
+        <x:v>connection_help</x:v>
+      </x:c>
+      <x:c r="B77" s="45" t="str">
+        <x:v>서버 연결 상태를 확인한 후 다시 시도해 주세요.</x:v>
+      </x:c>
+      <x:c r="C77" s="45" t="str">
+        <x:v>Check the server connection and try again.</x:v>
+      </x:c>
+      <x:c r="D77" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="52" customHeight="1">
+      <x:c r="A78" s="45" t="str">
+        <x:v>room_capacity_too_small</x:v>
+      </x:c>
+      <x:c r="B78" s="45" t="str">
+        <x:v>현재 참가 인원보다 작게 설정할 수 없습니다.</x:v>
+      </x:c>
+      <x:c r="C78" s="45" t="str">
+        <x:v>Capacity cannot be smaller than the current player count.</x:v>
+      </x:c>
+      <x:c r="D78" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="52" customHeight="1">
+      <x:c r="A79" s="45" t="str">
+        <x:v>match_in_progress</x:v>
+      </x:c>
+      <x:c r="B79" s="45" t="str">
+        <x:v>이미 진행 중인 경기입니다.</x:v>
+      </x:c>
+      <x:c r="C79" s="45" t="str">
+        <x:v>This match is already in progress.</x:v>
+      </x:c>
+      <x:c r="D79" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="52" customHeight="1">
+      <x:c r="A80" s="45" t="str">
+        <x:v>host_only</x:v>
+      </x:c>
+      <x:c r="B80" s="45" t="str">
+        <x:v>방장만 실행할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="C80" s="45" t="str">
+        <x:v>Only the host can do this.</x:v>
+      </x:c>
+      <x:c r="D80" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="52" customHeight="1">
+      <x:c r="A81" s="45" t="str">
+        <x:v>map_meadow</x:v>
+      </x:c>
+      <x:c r="B81" s="45" t="str">
+        <x:v>바람 초원</x:v>
+      </x:c>
+      <x:c r="C81" s="45" t="str">
+        <x:v>WIND MEADOW</x:v>
+      </x:c>
+      <x:c r="D81" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="52" customHeight="1">
+      <x:c r="A82" s="45" t="str">
+        <x:v>map_meadow_desc</x:v>
+      </x:c>
+      <x:c r="B82" s="45" t="str">
+        <x:v>동일 높이의 시작 발판과 완만한 엄폐 언덕</x:v>
+      </x:c>
+      <x:c r="C82" s="45" t="str">
+        <x:v>Equal-height spawns with gentle cover slopes</x:v>
+      </x:c>
+      <x:c r="D82" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="52" customHeight="1">
+      <x:c r="A83" s="45" t="str">
+        <x:v>map_citadel</x:v>
+      </x:c>
+      <x:c r="B83" s="45" t="str">
+        <x:v>쌍둥이 성채</x:v>
+      </x:c>
+      <x:c r="C83" s="45" t="str">
+        <x:v>TWIN CITADELS</x:v>
+      </x:c>
+      <x:c r="D83" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="52" customHeight="1">
+      <x:c r="A84" s="45" t="str">
+        <x:v>map_citadel_desc</x:v>
+      </x:c>
+      <x:c r="B84" s="45" t="str">
+        <x:v>동일한 방어 발판, 파괴 가능한 아치와 지하 공간</x:v>
+      </x:c>
+      <x:c r="C84" s="45" t="str">
+        <x:v>Equal defensive platforms, breakable arches and cavities</x:v>
+      </x:c>
+      <x:c r="D84" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="52" customHeight="1">
+      <x:c r="A85" s="45" t="str">
+        <x:v>map_reef</x:v>
+      </x:c>
+      <x:c r="B85" s="45" t="str">
+        <x:v>조각섬 군도</x:v>
+      </x:c>
+      <x:c r="C85" s="45" t="str">
+        <x:v>SHATTERED REEF</x:v>
+      </x:c>
+      <x:c r="D85" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="52" customHeight="1">
+      <x:c r="A86" s="45" t="str">
+        <x:v>map_reef_desc</x:v>
+      </x:c>
+      <x:c r="B86" s="45" t="str">
+        <x:v>네 개의 동일 높이 섬과 좁은 도약 구간</x:v>
+      </x:c>
+      <x:c r="C86" s="45" t="str">
+        <x:v>Four equal-height islands with narrow jump gaps</x:v>
+      </x:c>
+      <x:c r="D86" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="52" customHeight="1">
+      <x:c r="A87" s="45" t="str">
+        <x:v>map_select</x:v>
+      </x:c>
+      <x:c r="B87" s="45" t="str">
+        <x:v>전장 선택</x:v>
+      </x:c>
+      <x:c r="C87" s="45" t="str">
+        <x:v>BATTLEFIELD</x:v>
+      </x:c>
+      <x:c r="D87" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="52" customHeight="1">
+      <x:c r="A88" s="45" t="str">
+        <x:v>choose_character</x:v>
+      </x:c>
+      <x:c r="B88" s="45" t="str">
+        <x:v>캐릭터 선택</x:v>
+      </x:c>
+      <x:c r="C88" s="45" t="str">
+        <x:v>CHOOSE A CHARACTER</x:v>
+      </x:c>
+      <x:c r="D88" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="52" customHeight="1">
+      <x:c r="A89" s="45" t="str">
+        <x:v>turn_player</x:v>
+      </x:c>
+      <x:c r="B89" s="45" t="str">
+        <x:v>P{0}의 턴 · {1} 라운드</x:v>
+      </x:c>
+      <x:c r="C89" s="45" t="str">
+        <x:v>P{0}'S TURN · ROUND {1}</x:v>
+      </x:c>
+      <x:c r="D89" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="52" customHeight="1">
+      <x:c r="A90" s="45" t="str">
+        <x:v>loading_battle</x:v>
+      </x:c>
+      <x:c r="B90" s="45" t="str">
+        <x:v>전장을 준비하는 중...</x:v>
+      </x:c>
+      <x:c r="C90" s="45" t="str">
+        <x:v>Preparing the battlefield...</x:v>
+      </x:c>
+      <x:c r="D90" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="52" customHeight="1">
+      <x:c r="A91" s="45" t="str">
+        <x:v>timer_turn</x:v>
+      </x:c>
+      <x:c r="B91" s="45" t="str">
+        <x:v>턴 남은 시간  {0:0.0}초</x:v>
+      </x:c>
+      <x:c r="C91" s="45" t="str">
+        <x:v>TURN  {0:0.0}s</x:v>
+      </x:c>
+      <x:c r="D91" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="52" customHeight="1">
+      <x:c r="A92" s="45" t="str">
+        <x:v>timer_residual</x:v>
+      </x:c>
+      <x:c r="B92" s="45" t="str">
+        <x:v>이동 남은 시간  {0:0.0}초</x:v>
+      </x:c>
+      <x:c r="C92" s="45" t="str">
+        <x:v>MOVEMENT  {0:0.0}s</x:v>
+      </x:c>
+      <x:c r="D92" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="52" customHeight="1">
+      <x:c r="A93" s="45" t="str">
+        <x:v>timer_settlement</x:v>
+      </x:c>
+      <x:c r="B93" s="45" t="str">
+        <x:v>피해 정산  {0:0.0}초</x:v>
+      </x:c>
+      <x:c r="C93" s="45" t="str">
+        <x:v>RESOLVING  {0:0.0}s</x:v>
+      </x:c>
+      <x:c r="D93" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="52" customHeight="1">
+      <x:c r="A94" s="45" t="str">
+        <x:v>cooldown_rounds</x:v>
+      </x:c>
+      <x:c r="B94" s="45" t="str">
+        <x:v>대기 {0}</x:v>
+      </x:c>
+      <x:c r="C94" s="45" t="str">
+        <x:v>WAIT {0}</x:v>
+      </x:c>
+      <x:c r="D94" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="52" customHeight="1">
+      <x:c r="A95" s="45" t="str">
+        <x:v>empty_slot</x:v>
+      </x:c>
+      <x:c r="B95" s="45" t="str">
+        <x:v>비어 있음</x:v>
+      </x:c>
+      <x:c r="C95" s="45" t="str">
+        <x:v>EMPTY</x:v>
+      </x:c>
+      <x:c r="D95" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="52" customHeight="1">
+      <x:c r="A96" s="45" t="str">
+        <x:v>end_turn</x:v>
+      </x:c>
+      <x:c r="B96" s="45" t="str">
+        <x:v>턴 종료</x:v>
+      </x:c>
+      <x:c r="C96" s="45" t="str">
+        <x:v>END TURN</x:v>
+      </x:c>
+      <x:c r="D96" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="52" customHeight="1">
+      <x:c r="A97" s="45" t="str">
+        <x:v>battle_menu</x:v>
+      </x:c>
+      <x:c r="B97" s="45" t="str">
+        <x:v>메뉴</x:v>
+      </x:c>
+      <x:c r="C97" s="45" t="str">
+        <x:v>MENU</x:v>
+      </x:c>
+      <x:c r="D97" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="52" customHeight="1">
+      <x:c r="A98" s="45" t="str">
+        <x:v>resume</x:v>
+      </x:c>
+      <x:c r="B98" s="45" t="str">
+        <x:v>계속하기</x:v>
+      </x:c>
+      <x:c r="C98" s="45" t="str">
+        <x:v>RESUME</x:v>
+      </x:c>
+      <x:c r="D98" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="52" customHeight="1">
+      <x:c r="A99" s="45" t="str">
+        <x:v>return_title</x:v>
+      </x:c>
+      <x:c r="B99" s="45" t="str">
+        <x:v>타이틀로 나가기</x:v>
+      </x:c>
+      <x:c r="C99" s="45" t="str">
+        <x:v>LEAVE TO TITLE</x:v>
+      </x:c>
+      <x:c r="D99" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="52" customHeight="1">
+      <x:c r="A100" s="45" t="str">
+        <x:v>match_winner</x:v>
+      </x:c>
+      <x:c r="B100" s="45" t="str">
+        <x:v>P{0} 팀 승리!</x:v>
+      </x:c>
+      <x:c r="C100" s="45" t="str">
+        <x:v>P{0} WINS!</x:v>
+      </x:c>
+      <x:c r="D100" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="52" customHeight="1">
+      <x:c r="A101" s="45" t="str">
+        <x:v>match_draw</x:v>
+      </x:c>
+      <x:c r="B101" s="45" t="str">
+        <x:v>무승부</x:v>
+      </x:c>
+      <x:c r="C101" s="45" t="str">
+        <x:v>DRAW</x:v>
+      </x:c>
+      <x:c r="D101" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="52" customHeight="1">
+      <x:c r="A102" s="45" t="str">
+        <x:v>result_online</x:v>
+      </x:c>
+      <x:c r="B102" s="45" t="str">
+        <x:v>방장이 로비로 돌아가기를 선택하면 같은 방에서 다시 편성할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="C102" s="45" t="str">
+        <x:v>The host can return everyone to the lobby for another match.</x:v>
+      </x:c>
+      <x:c r="D102" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="52" customHeight="1">
+      <x:c r="A103" s="45" t="str">
+        <x:v>result_local</x:v>
+      </x:c>
+      <x:c r="B103" s="45" t="str">
+        <x:v>같은 팀으로 재경기하거나 타이틀에서 다시 편성하세요.</x:v>
+      </x:c>
+      <x:c r="C103" s="45" t="str">
+        <x:v>Play again with these squads or choose new squads from the title.</x:v>
+      </x:c>
+      <x:c r="D103" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="52" customHeight="1">
+      <x:c r="A104" s="45" t="str">
+        <x:v>replay</x:v>
+      </x:c>
+      <x:c r="B104" s="45" t="str">
+        <x:v>재경기 / 로비로</x:v>
+      </x:c>
+      <x:c r="C104" s="45" t="str">
+        <x:v>PLAY AGAIN / LOBBY</x:v>
+      </x:c>
+      <x:c r="D104" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="52" customHeight="1">
+      <x:c r="A105" s="45" t="str">
+        <x:v>connection_lost</x:v>
+      </x:c>
+      <x:c r="B105" s="45" t="str">
+        <x:v>서버 연결이 끊어졌습니다</x:v>
+      </x:c>
+      <x:c r="C105" s="45" t="str">
+        <x:v>CONNECTION LOST</x:v>
+      </x:c>
+      <x:c r="D105" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="52" customHeight="1">
+      <x:c r="A106" s="45" t="str">
+        <x:v>player_disconnected</x:v>
+      </x:c>
+      <x:c r="B106" s="45" t="str">
+        <x:v>참가자의 연결이 끊어졌습니다</x:v>
+      </x:c>
+      <x:c r="C106" s="45" t="str">
+        <x:v>A PLAYER DISCONNECTED</x:v>
+      </x:c>
+      <x:c r="D106" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="52" customHeight="1">
+      <x:c r="A107" s="45" t="str">
+        <x:v>disconnect_return</x:v>
+      </x:c>
+      <x:c r="B107" s="45" t="str">
+        <x:v>타이틀로 돌아가서 다시 접속해 주세요.</x:v>
+      </x:c>
+      <x:c r="C107" s="45" t="str">
+        <x:v>Return to the title to reconnect.</x:v>
+      </x:c>
+      <x:c r="D107" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="52" customHeight="1">
+      <x:c r="A108" s="45" t="str">
+        <x:v>team_health</x:v>
+      </x:c>
+      <x:c r="B108" s="45" t="str">
+        <x:v>팀 체력</x:v>
+      </x:c>
+      <x:c r="C108" s="45" t="str">
+        <x:v>SQUAD HEALTH</x:v>
+      </x:c>
+      <x:c r="D108" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="52" customHeight="1">
+      <x:c r="A109" s="45" t="str">
+        <x:v>battle_skills</x:v>
+      </x:c>
+      <x:c r="B109" s="45" t="str">
+        <x:v>고유 머리</x:v>
+      </x:c>
+      <x:c r="C109" s="45" t="str">
+        <x:v>SKILLS</x:v>
+      </x:c>
+      <x:c r="D109" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="52" customHeight="1">
+      <x:c r="A110" s="45" t="str">
+        <x:v>battle_common</x:v>
+      </x:c>
+      <x:c r="B110" s="45" t="str">
+        <x:v>공용 머리</x:v>
+      </x:c>
+      <x:c r="C110" s="45" t="str">
+        <x:v>COMMON HEADS</x:v>
+      </x:c>
+      <x:c r="D110" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="52" customHeight="1">
+      <x:c r="A111" s="45" t="str">
+        <x:v>charge_power</x:v>
+      </x:c>
+      <x:c r="B111" s="45" t="str">
+        <x:v>차징</x:v>
+      </x:c>
+      <x:c r="C111" s="45" t="str">
+        <x:v>POWER</x:v>
+      </x:c>
+      <x:c r="D111" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="52" customHeight="1">
+      <x:c r="A112" s="45" t="str">
+        <x:v>brand_eyebrow</x:v>
+      </x:c>
+      <x:c r="B112" s="45" t="str">
+        <x:v>지형이 바뀌는 턴제 포격 대전</x:v>
+      </x:c>
+      <x:c r="C112" s="45" t="str">
+        <x:v>TURN-BASED TERRAIN BATTLES</x:v>
+      </x:c>
+      <x:c r="D112" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="52" customHeight="1">
+      <x:c r="A113" s="45" t="str">
+        <x:v>menu_hint</x:v>
+      </x:c>
+      <x:c r="B113" s="45" t="str">
+        <x:v>2인·4인 대전 · 캐릭터를 고르고 전장을 바꾸세요</x:v>
+      </x:c>
+      <x:c r="C113" s="45" t="str">
+        <x:v>2 or 4 players · Choose your crew, reshape the battlefield</x:v>
+      </x:c>
+      <x:c r="D113" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="52" customHeight="1">
+      <x:c r="A114" s="45" t="str">
+        <x:v>menu_warning</x:v>
+      </x:c>
+      <x:c r="B114" s="45" t="str">
+        <x:v>개발 테스트 버전 · 온라인은 서버 연결이 필요합니다.</x:v>
+      </x:c>
+      <x:c r="C114" s="45" t="str">
+        <x:v>Development test build · Online requires a server.</x:v>
+      </x:c>
+      <x:c r="D114" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="52" customHeight="1">
+      <x:c r="A115" s="45" t="str">
+        <x:v>not_ready_reason</x:v>
+      </x:c>
+      <x:c r="B115" s="45" t="str">
+        <x:v>참가자 전원이 팀 선택과 준비를 완료해야 합니다.</x:v>
+      </x:c>
+      <x:c r="C115" s="45" t="str">
+        <x:v>Everyone must select a squad and be ready.</x:v>
+      </x:c>
+      <x:c r="D115" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="52" customHeight="1">
+      <x:c r="A116" s="45" t="str">
+        <x:v>menu_online</x:v>
+      </x:c>
+      <x:c r="B116" s="45" t="str">
+        <x:v>온라인 대전</x:v>
+      </x:c>
+      <x:c r="C116" s="45" t="str">
+        <x:v>ONLINE PLAY</x:v>
+      </x:c>
+      <x:c r="D116" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="52" customHeight="1">
+      <x:c r="A117" s="45" t="str">
+        <x:v>menu_local</x:v>
+      </x:c>
+      <x:c r="B117" s="45" t="str">
+        <x:v>로컬 대전</x:v>
+      </x:c>
+      <x:c r="C117" s="45" t="str">
+        <x:v>LOCAL PLAY</x:v>
+      </x:c>
+      <x:c r="D117" s="45" t="str">
+        <x:v>0916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="44" t="str">
+        <x:v>mode_duel</x:v>
+      </x:c>
+      <x:c r="B118" s="44" t="str">
+        <x:v>2인 개인전</x:v>
+      </x:c>
+      <x:c r="C118" s="44" t="str">
+        <x:v>2 players · Duel</x:v>
+      </x:c>
+      <x:c r="D118" s="44" t="str">
+        <x:v>0916 모드 변경</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="44" t="str">
+        <x:v>mode_ffa</x:v>
+      </x:c>
+      <x:c r="B119" s="44" t="str">
+        <x:v>4인 개인전</x:v>
+      </x:c>
+      <x:c r="C119" s="44" t="str">
+        <x:v>4 players · FFA</x:v>
+      </x:c>
+      <x:c r="D119" s="44" t="str">
+        <x:v>0916 모드 변경</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="44" t="str">
+        <x:v>mode_teams</x:v>
+      </x:c>
+      <x:c r="B120" s="44" t="str">
+        <x:v>4인 2대2</x:v>
+      </x:c>
+      <x:c r="C120" s="44" t="str">
+        <x:v>4 players · 2v2</x:v>
+      </x:c>
+      <x:c r="D120" s="44" t="str">
+        <x:v>0916 모드 변경</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="44" t="str">
+        <x:v>mode_select</x:v>
+      </x:c>
+      <x:c r="B121" s="44" t="str">
+        <x:v>게임 모드</x:v>
+      </x:c>
+      <x:c r="C121" s="44" t="str">
+        <x:v>GAME MODE</x:v>
+      </x:c>
+      <x:c r="D121" s="44" t="str">
+        <x:v>0916 모드 변경</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="44" t="str">
+        <x:v>alliance_label</x:v>
+      </x:c>
+      <x:c r="B122" s="44" t="str">
+        <x:v>팀 {0}</x:v>
+      </x:c>
+      <x:c r="C122" s="44" t="str">
+        <x:v>Team {0}</x:v>
+      </x:c>
+      <x:c r="D122" s="44" t="str">
+        <x:v>0916 모드 변경</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="44" t="str">
+        <x:v>team_winner</x:v>
+      </x:c>
+      <x:c r="B123" s="44" t="str">
+        <x:v>팀 {0} 승리!</x:v>
+      </x:c>
+      <x:c r="C123" s="44" t="str">
+        <x:v>Team {0} wins!</x:v>
+      </x:c>
+      <x:c r="D123" s="44" t="str">
+        <x:v>0916 모드 변경</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="44" t="str">
+        <x:v>unsupported_mode</x:v>
+      </x:c>
+      <x:c r="B124" s="44" t="str">
+        <x:v>지원하지 않는 게임 모드입니다.</x:v>
+      </x:c>
+      <x:c r="C124" s="44" t="str">
+        <x:v>Unsupported game mode.</x:v>
+      </x:c>
+      <x:c r="D124" s="44" t="str">
+        <x:v>0916 모드 변경</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="44" t="str">
+        <x:v>team_rule_hint</x:v>
+      </x:c>
+      <x:c r="B125" s="44" t="str">
+        <x:v>2대2: P1·P3 / P2·P4가 한 팀이며, 아군 피해가 적용됩니다.</x:v>
+      </x:c>
+      <x:c r="C125" s="44" t="str">
+        <x:v>2v2: P1 &amp; P3 vs P2 &amp; P4. Friendly fire is enabled.</x:v>
+      </x:c>
+      <x:c r="D125" s="44" t="str">
+        <x:v>0916 모드 변경</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
@@ -1298,7 +2286,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c127453a37049b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5d87d00f26640ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3481,7 +4469,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87862c51b9794dcd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d3aedd762984575"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/Assets/GameData/ObjectHeadData.xlsx
+++ b/Assets/GameData/ObjectHeadData.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="번역" sheetId="1" r:id="Rc940989237ed4c19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수치" sheetId="2" r:id="R253d0154945f4121"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계산기" sheetId="3" r:id="R76a4586707144050"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="번역" sheetId="1" r:id="R66f70e607fd04cd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수치" sheetId="2" r:id="Rfc528d129e054c7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계산기" sheetId="3" r:id="R29069b44b8594611"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -308,7 +308,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LocalizationTable" displayName="LocalizationTable" ref="A4:D125" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LocalizationTable" displayName="LocalizationTable" ref="A4:D168" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="key"/>
     <x:tableColumn id="2" name="한국어"/>
@@ -320,7 +320,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="BalanceTable" displayName="BalanceTable" ref="A4:F110" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="BalanceTable" displayName="BalanceTable" ref="A4:F174" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="key"/>
     <x:tableColumn id="2" name="분류"/>
@@ -2279,6 +2279,608 @@
         <x:v>0916 모드 변경</x:v>
       </x:c>
     </x:row>
+    <x:row r="126" ht="46" customHeight="1">
+      <x:c r="A126" s="45" t="str">
+        <x:v>menu_play</x:v>
+      </x:c>
+      <x:c r="B126" s="45" t="str">
+        <x:v>게임 시작</x:v>
+      </x:c>
+      <x:c r="C126" s="45" t="str">
+        <x:v>Play</x:v>
+      </x:c>
+      <x:c r="D126" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="46" customHeight="1">
+      <x:c r="A127" s="45" t="str">
+        <x:v>menu_settings</x:v>
+      </x:c>
+      <x:c r="B127" s="45" t="str">
+        <x:v>설정</x:v>
+      </x:c>
+      <x:c r="C127" s="45" t="str">
+        <x:v>Settings</x:v>
+      </x:c>
+      <x:c r="D127" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="46" customHeight="1">
+      <x:c r="A128" s="45" t="str">
+        <x:v>find_room</x:v>
+      </x:c>
+      <x:c r="B128" s="45" t="str">
+        <x:v>방 찾기</x:v>
+      </x:c>
+      <x:c r="C128" s="45" t="str">
+        <x:v>Find a room</x:v>
+      </x:c>
+      <x:c r="D128" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="46" customHeight="1">
+      <x:c r="A129" s="45" t="str">
+        <x:v>training</x:v>
+      </x:c>
+      <x:c r="B129" s="45" t="str">
+        <x:v>훈련장</x:v>
+      </x:c>
+      <x:c r="C129" s="45" t="str">
+        <x:v>Training</x:v>
+      </x:c>
+      <x:c r="D129" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="46" customHeight="1">
+      <x:c r="A130" s="45" t="str">
+        <x:v>back</x:v>
+      </x:c>
+      <x:c r="B130" s="45" t="str">
+        <x:v>뒤로</x:v>
+      </x:c>
+      <x:c r="C130" s="45" t="str">
+        <x:v>Back</x:v>
+      </x:c>
+      <x:c r="D130" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="46" customHeight="1">
+      <x:c r="A131" s="45" t="str">
+        <x:v>confirm</x:v>
+      </x:c>
+      <x:c r="B131" s="45" t="str">
+        <x:v>확인</x:v>
+      </x:c>
+      <x:c r="C131" s="45" t="str">
+        <x:v>Confirm</x:v>
+      </x:c>
+      <x:c r="D131" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="46" customHeight="1">
+      <x:c r="A132" s="45" t="str">
+        <x:v>join_code_hint</x:v>
+      </x:c>
+      <x:c r="B132" s="45" t="str">
+        <x:v>친구에게 받은 6자리 방 코드를 입력하세요.</x:v>
+      </x:c>
+      <x:c r="C132" s="45" t="str">
+        <x:v>Enter the six-character room code from your friend.</x:v>
+      </x:c>
+      <x:c r="D132" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="46" customHeight="1">
+      <x:c r="A133" s="45" t="str">
+        <x:v>resolution</x:v>
+      </x:c>
+      <x:c r="B133" s="45" t="str">
+        <x:v>해상도</x:v>
+      </x:c>
+      <x:c r="C133" s="45" t="str">
+        <x:v>Resolution</x:v>
+      </x:c>
+      <x:c r="D133" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="46" customHeight="1">
+      <x:c r="A134" s="45" t="str">
+        <x:v>window_mode</x:v>
+      </x:c>
+      <x:c r="B134" s="45" t="str">
+        <x:v>화면 모드</x:v>
+      </x:c>
+      <x:c r="C134" s="45" t="str">
+        <x:v>Display mode</x:v>
+      </x:c>
+      <x:c r="D134" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="46" customHeight="1">
+      <x:c r="A135" s="45" t="str">
+        <x:v>language</x:v>
+      </x:c>
+      <x:c r="B135" s="45" t="str">
+        <x:v>언어</x:v>
+      </x:c>
+      <x:c r="C135" s="45" t="str">
+        <x:v>Language</x:v>
+      </x:c>
+      <x:c r="D135" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="46" customHeight="1">
+      <x:c r="A136" s="45" t="str">
+        <x:v>volume_bgm</x:v>
+      </x:c>
+      <x:c r="B136" s="45" t="str">
+        <x:v>배경음악</x:v>
+      </x:c>
+      <x:c r="C136" s="45" t="str">
+        <x:v>Music</x:v>
+      </x:c>
+      <x:c r="D136" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="46" customHeight="1">
+      <x:c r="A137" s="45" t="str">
+        <x:v>volume_sfx</x:v>
+      </x:c>
+      <x:c r="B137" s="45" t="str">
+        <x:v>효과음</x:v>
+      </x:c>
+      <x:c r="C137" s="45" t="str">
+        <x:v>Sound effects</x:v>
+      </x:c>
+      <x:c r="D137" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="46" customHeight="1">
+      <x:c r="A138" s="45" t="str">
+        <x:v>windowed</x:v>
+      </x:c>
+      <x:c r="B138" s="45" t="str">
+        <x:v>창 모드</x:v>
+      </x:c>
+      <x:c r="C138" s="45" t="str">
+        <x:v>Windowed</x:v>
+      </x:c>
+      <x:c r="D138" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="46" customHeight="1">
+      <x:c r="A139" s="45" t="str">
+        <x:v>borderless</x:v>
+      </x:c>
+      <x:c r="B139" s="45" t="str">
+        <x:v>테두리 없는 창</x:v>
+      </x:c>
+      <x:c r="C139" s="45" t="str">
+        <x:v>Borderless</x:v>
+      </x:c>
+      <x:c r="D139" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="46" customHeight="1">
+      <x:c r="A140" s="45" t="str">
+        <x:v>fullscreen</x:v>
+      </x:c>
+      <x:c r="B140" s="45" t="str">
+        <x:v>전체 화면</x:v>
+      </x:c>
+      <x:c r="C140" s="45" t="str">
+        <x:v>Fullscreen</x:v>
+      </x:c>
+      <x:c r="D140" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="46" customHeight="1">
+      <x:c r="A141" s="45" t="str">
+        <x:v>confirm_display</x:v>
+      </x:c>
+      <x:c r="B141" s="45" t="str">
+        <x:v>이 설정을 유지할까요? {0}초 뒤 원래대로 돌아갑니다.</x:v>
+      </x:c>
+      <x:c r="C141" s="45" t="str">
+        <x:v>Keep these settings? Reverting in {0}s.</x:v>
+      </x:c>
+      <x:c r="D141" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="46" customHeight="1">
+      <x:c r="A142" s="45" t="str">
+        <x:v>settings_saved</x:v>
+      </x:c>
+      <x:c r="B142" s="45" t="str">
+        <x:v>설정을 저장했습니다.</x:v>
+      </x:c>
+      <x:c r="C142" s="45" t="str">
+        <x:v>Settings saved.</x:v>
+      </x:c>
+      <x:c r="D142" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="46" customHeight="1">
+      <x:c r="A143" s="45" t="str">
+        <x:v>role_all</x:v>
+      </x:c>
+      <x:c r="B143" s="45" t="str">
+        <x:v>전체 역할</x:v>
+      </x:c>
+      <x:c r="C143" s="45" t="str">
+        <x:v>All roles</x:v>
+      </x:c>
+      <x:c r="D143" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="46" customHeight="1">
+      <x:c r="A144" s="45" t="str">
+        <x:v>role_damage</x:v>
+      </x:c>
+      <x:c r="B144" s="45" t="str">
+        <x:v>공격</x:v>
+      </x:c>
+      <x:c r="C144" s="45" t="str">
+        <x:v>Damage</x:v>
+      </x:c>
+      <x:c r="D144" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="46" customHeight="1">
+      <x:c r="A145" s="45" t="str">
+        <x:v>role_control</x:v>
+      </x:c>
+      <x:c r="B145" s="45" t="str">
+        <x:v>지역·위치 제어</x:v>
+      </x:c>
+      <x:c r="C145" s="45" t="str">
+        <x:v>Control</x:v>
+      </x:c>
+      <x:c r="D145" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="46" customHeight="1">
+      <x:c r="A146" s="45" t="str">
+        <x:v>role_support</x:v>
+      </x:c>
+      <x:c r="B146" s="45" t="str">
+        <x:v>공격·지원</x:v>
+      </x:c>
+      <x:c r="C146" s="45" t="str">
+        <x:v>Support</x:v>
+      </x:c>
+      <x:c r="D146" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="46" customHeight="1">
+      <x:c r="A147" s="45" t="str">
+        <x:v>roster_count</x:v>
+      </x:c>
+      <x:c r="B147" s="45" t="str">
+        <x:v>{0} / {1}종</x:v>
+      </x:c>
+      <x:c r="C147" s="45" t="str">
+        <x:v>{0} / {1}</x:v>
+      </x:c>
+      <x:c r="D147" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="46" customHeight="1">
+      <x:c r="A148" s="45" t="str">
+        <x:v>search_character</x:v>
+      </x:c>
+      <x:c r="B148" s="45" t="str">
+        <x:v>캐릭터 이름 검색</x:v>
+      </x:c>
+      <x:c r="C148" s="45" t="str">
+        <x:v>Search characters</x:v>
+      </x:c>
+      <x:c r="D148" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="46" customHeight="1">
+      <x:c r="A149" s="45" t="str">
+        <x:v>revolver_name</x:v>
+      </x:c>
+      <x:c r="B149" s="45" t="str">
+        <x:v>리볼버</x:v>
+      </x:c>
+      <x:c r="C149" s="45" t="str">
+        <x:v>Revolver</x:v>
+      </x:c>
+      <x:c r="D149" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="46" customHeight="1">
+      <x:c r="A150" s="45" t="str">
+        <x:v>revolver_description</x:v>
+      </x:c>
+      <x:c r="B150" s="45" t="str">
+        <x:v>직선 사격, 적도 치유하는 녹색 플레어, 아군도 맞는 공습으로 전장을 지원합니다.</x:v>
+      </x:c>
+      <x:c r="C150" s="45" t="str">
+        <x:v>Straight shots, an all-team healing flare, and friendly-fire airstrikes.</x:v>
+      </x:c>
+      <x:c r="D150" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="46" customHeight="1">
+      <x:c r="A151" s="45" t="str">
+        <x:v>magnet_name</x:v>
+      </x:c>
+      <x:c r="B151" s="45" t="str">
+        <x:v>자석</x:v>
+      </x:c>
+      <x:c r="C151" s="45" t="str">
+        <x:v>Magnet</x:v>
+      </x:c>
+      <x:c r="D151" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="46" customHeight="1">
+      <x:c r="A152" s="45" t="str">
+        <x:v>magnet_description</x:v>
+      </x:c>
+      <x:c r="B152" s="45" t="str">
+        <x:v>인력으로 모으고 척력으로 밀어냅니다. 아군도 영향받으니 위치를 주의하세요.</x:v>
+      </x:c>
+      <x:c r="C152" s="45" t="str">
+        <x:v>Gather with attraction and scatter with repulsion. Allies are affected too.</x:v>
+      </x:c>
+      <x:c r="D152" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="46" customHeight="1">
+      <x:c r="A153" s="45" t="str">
+        <x:v>kettle_name</x:v>
+      </x:c>
+      <x:c r="B153" s="45" t="str">
+        <x:v>주전자</x:v>
+      </x:c>
+      <x:c r="C153" s="45" t="str">
+        <x:v>Kettle</x:v>
+      </x:c>
+      <x:c r="D153" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="46" customHeight="1">
+      <x:c r="A154" s="45" t="str">
+        <x:v>kettle_description</x:v>
+      </x:c>
+      <x:c r="B154" s="45" t="str">
+        <x:v>온수로 주변을 치유하고, 증기로 길을 막고, 압력 폭발로 지형을 부숩니다.</x:v>
+      </x:c>
+      <x:c r="C154" s="45" t="str">
+        <x:v>Heal with warm water, control paths with steam, and break terrain with pressure.</x:v>
+      </x:c>
+      <x:c r="D154" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="46" customHeight="1">
+      <x:c r="A155" s="45" t="str">
+        <x:v>common_potion</x:v>
+      </x:c>
+      <x:c r="B155" s="45" t="str">
+        <x:v>치유 포션</x:v>
+      </x:c>
+      <x:c r="C155" s="45" t="str">
+        <x:v>Healing potion</x:v>
+      </x:c>
+      <x:c r="D155" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="46" customHeight="1">
+      <x:c r="A156" s="45" t="str">
+        <x:v>common_ice</x:v>
+      </x:c>
+      <x:c r="B156" s="45" t="str">
+        <x:v>얼음 머리</x:v>
+      </x:c>
+      <x:c r="C156" s="45" t="str">
+        <x:v>Ice head</x:v>
+      </x:c>
+      <x:c r="D156" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="46" customHeight="1">
+      <x:c r="A157" s="45" t="str">
+        <x:v>common_helmet</x:v>
+      </x:c>
+      <x:c r="B157" s="45" t="str">
+        <x:v>철제 헬멧</x:v>
+      </x:c>
+      <x:c r="C157" s="45" t="str">
+        <x:v>Iron helmet</x:v>
+      </x:c>
+      <x:c r="D157" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="46" customHeight="1">
+      <x:c r="A158" s="45" t="str">
+        <x:v>common_smoke</x:v>
+      </x:c>
+      <x:c r="B158" s="45" t="str">
+        <x:v>연막 머리</x:v>
+      </x:c>
+      <x:c r="C158" s="45" t="str">
+        <x:v>Smoke head</x:v>
+      </x:c>
+      <x:c r="D158" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="46" customHeight="1">
+      <x:c r="A159" s="45" t="str">
+        <x:v>revolver_skill_1</x:v>
+      </x:c>
+      <x:c r="B159" s="45" t="str">
+        <x:v>직선 사격</x:v>
+      </x:c>
+      <x:c r="C159" s="45" t="str">
+        <x:v>Straight shot</x:v>
+      </x:c>
+      <x:c r="D159" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="46" customHeight="1">
+      <x:c r="A160" s="45" t="str">
+        <x:v>revolver_skill_2</x:v>
+      </x:c>
+      <x:c r="B160" s="45" t="str">
+        <x:v>구호 플레어</x:v>
+      </x:c>
+      <x:c r="C160" s="45" t="str">
+        <x:v>Relief flare</x:v>
+      </x:c>
+      <x:c r="D160" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="46" customHeight="1">
+      <x:c r="A161" s="45" t="str">
+        <x:v>revolver_skill_3</x:v>
+      </x:c>
+      <x:c r="B161" s="45" t="str">
+        <x:v>공습 신호</x:v>
+      </x:c>
+      <x:c r="C161" s="45" t="str">
+        <x:v>Airstrike signal</x:v>
+      </x:c>
+      <x:c r="D161" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="46" customHeight="1">
+      <x:c r="A162" s="45" t="str">
+        <x:v>magnet_skill_1</x:v>
+      </x:c>
+      <x:c r="B162" s="45" t="str">
+        <x:v>인력탄</x:v>
+      </x:c>
+      <x:c r="C162" s="45" t="str">
+        <x:v>Attraction</x:v>
+      </x:c>
+      <x:c r="D162" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="46" customHeight="1">
+      <x:c r="A163" s="45" t="str">
+        <x:v>magnet_skill_2</x:v>
+      </x:c>
+      <x:c r="B163" s="45" t="str">
+        <x:v>척력탄</x:v>
+      </x:c>
+      <x:c r="C163" s="45" t="str">
+        <x:v>Repulsion</x:v>
+      </x:c>
+      <x:c r="D163" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="46" customHeight="1">
+      <x:c r="A164" s="45" t="str">
+        <x:v>magnet_skill_3</x:v>
+      </x:c>
+      <x:c r="B164" s="45" t="str">
+        <x:v>전자석 펄스</x:v>
+      </x:c>
+      <x:c r="C164" s="45" t="str">
+        <x:v>Electromagnetic pulse</x:v>
+      </x:c>
+      <x:c r="D164" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="46" customHeight="1">
+      <x:c r="A165" s="45" t="str">
+        <x:v>kettle_skill_1</x:v>
+      </x:c>
+      <x:c r="B165" s="45" t="str">
+        <x:v>따뜻한 한 잔</x:v>
+      </x:c>
+      <x:c r="C165" s="45" t="str">
+        <x:v>Warm water</x:v>
+      </x:c>
+      <x:c r="D165" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="46" customHeight="1">
+      <x:c r="A166" s="45" t="str">
+        <x:v>kettle_skill_2</x:v>
+      </x:c>
+      <x:c r="B166" s="45" t="str">
+        <x:v>증기 지대</x:v>
+      </x:c>
+      <x:c r="C166" s="45" t="str">
+        <x:v>Steam zone</x:v>
+      </x:c>
+      <x:c r="D166" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="46" customHeight="1">
+      <x:c r="A167" s="45" t="str">
+        <x:v>kettle_skill_3</x:v>
+      </x:c>
+      <x:c r="B167" s="45" t="str">
+        <x:v>압력 폭발</x:v>
+      </x:c>
+      <x:c r="C167" s="45" t="str">
+        <x:v>Pressure burst</x:v>
+      </x:c>
+      <x:c r="D167" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="46" customHeight="1">
+      <x:c r="A168" s="45" t="str">
+        <x:v>reset_training</x:v>
+      </x:c>
+      <x:c r="B168" s="45" t="str">
+        <x:v>훈련장 초기화</x:v>
+      </x:c>
+      <x:c r="C168" s="45" t="str">
+        <x:v>Reset training</x:v>
+      </x:c>
+      <x:c r="D168" s="45" t="str">
+        <x:v>0916 확장</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
@@ -2286,7 +2888,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5d87d00f26640ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb404f63f469f4691"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4462,6 +5064,1286 @@
         <x:v>미구현</x:v>
       </x:c>
     </x:row>
+    <x:row r="111" ht="26" customHeight="1">
+      <x:c r="A111" s="44" t="str">
+        <x:v>character.revolver.max_hp</x:v>
+      </x:c>
+      <x:c r="B111" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C111" s="44" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D111" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E111" s="44" t="str">
+        <x:v>최대 체력</x:v>
+      </x:c>
+      <x:c r="F111" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="26" customHeight="1">
+      <x:c r="A112" s="44" t="str">
+        <x:v>character.revolver.throw_power</x:v>
+      </x:c>
+      <x:c r="B112" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C112" s="44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D112" s="44" t="str">
+        <x:v>배율</x:v>
+      </x:c>
+      <x:c r="E112" s="44" t="str">
+        <x:v>투척력</x:v>
+      </x:c>
+      <x:c r="F112" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="26" customHeight="1">
+      <x:c r="A113" s="44" t="str">
+        <x:v>character.revolver.knockback_resistance</x:v>
+      </x:c>
+      <x:c r="B113" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C113" s="44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D113" s="44" t="str">
+        <x:v>배율</x:v>
+      </x:c>
+      <x:c r="E113" s="44" t="str">
+        <x:v>넉백 저항</x:v>
+      </x:c>
+      <x:c r="F113" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="26" customHeight="1">
+      <x:c r="A114" s="44" t="str">
+        <x:v>character.magnet.max_hp</x:v>
+      </x:c>
+      <x:c r="B114" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C114" s="44" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D114" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E114" s="44" t="str">
+        <x:v>최대 체력</x:v>
+      </x:c>
+      <x:c r="F114" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="26" customHeight="1">
+      <x:c r="A115" s="44" t="str">
+        <x:v>character.magnet.throw_power</x:v>
+      </x:c>
+      <x:c r="B115" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C115" s="44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D115" s="44" t="str">
+        <x:v>배율</x:v>
+      </x:c>
+      <x:c r="E115" s="44" t="str">
+        <x:v>투척력</x:v>
+      </x:c>
+      <x:c r="F115" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="26" customHeight="1">
+      <x:c r="A116" s="44" t="str">
+        <x:v>character.magnet.knockback_resistance</x:v>
+      </x:c>
+      <x:c r="B116" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C116" s="44" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="D116" s="44" t="str">
+        <x:v>배율</x:v>
+      </x:c>
+      <x:c r="E116" s="44" t="str">
+        <x:v>넉백 저항</x:v>
+      </x:c>
+      <x:c r="F116" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="26" customHeight="1">
+      <x:c r="A117" s="44" t="str">
+        <x:v>character.kettle.max_hp</x:v>
+      </x:c>
+      <x:c r="B117" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C117" s="44" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D117" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E117" s="44" t="str">
+        <x:v>최대 체력</x:v>
+      </x:c>
+      <x:c r="F117" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="26" customHeight="1">
+      <x:c r="A118" s="44" t="str">
+        <x:v>character.kettle.throw_power</x:v>
+      </x:c>
+      <x:c r="B118" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C118" s="44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D118" s="44" t="str">
+        <x:v>배율</x:v>
+      </x:c>
+      <x:c r="E118" s="44" t="str">
+        <x:v>투척력</x:v>
+      </x:c>
+      <x:c r="F118" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="26" customHeight="1">
+      <x:c r="A119" s="44" t="str">
+        <x:v>character.kettle.knockback_resistance</x:v>
+      </x:c>
+      <x:c r="B119" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C119" s="44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D119" s="44" t="str">
+        <x:v>배율</x:v>
+      </x:c>
+      <x:c r="E119" s="44" t="str">
+        <x:v>넉백 저항</x:v>
+      </x:c>
+      <x:c r="F119" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="26" customHeight="1">
+      <x:c r="A120" s="44" t="str">
+        <x:v>skill.revolver.1.max_damage</x:v>
+      </x:c>
+      <x:c r="B120" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C120" s="44" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D120" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E120" s="44" t="str">
+        <x:v>최대 피해</x:v>
+      </x:c>
+      <x:c r="F120" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="26" customHeight="1">
+      <x:c r="A121" s="44" t="str">
+        <x:v>skill.revolver.1.radius</x:v>
+      </x:c>
+      <x:c r="B121" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C121" s="44" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D121" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E121" s="44" t="str">
+        <x:v>효과 반경</x:v>
+      </x:c>
+      <x:c r="F121" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="26" customHeight="1">
+      <x:c r="A122" s="44" t="str">
+        <x:v>skill.revolver.1.speed</x:v>
+      </x:c>
+      <x:c r="B122" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C122" s="44" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D122" s="44" t="str">
+        <x:v>월드 단위/초</x:v>
+      </x:c>
+      <x:c r="E122" s="44" t="str">
+        <x:v>직선 탄속</x:v>
+      </x:c>
+      <x:c r="F122" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="26" customHeight="1">
+      <x:c r="A123" s="44" t="str">
+        <x:v>skill.revolver.1.cooldown</x:v>
+      </x:c>
+      <x:c r="B123" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C123" s="44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D123" s="44" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E123" s="44" t="str">
+        <x:v>재사용 대기</x:v>
+      </x:c>
+      <x:c r="F123" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="26" customHeight="1">
+      <x:c r="A124" s="44" t="str">
+        <x:v>skill.revolver.1.terrain_radius_px</x:v>
+      </x:c>
+      <x:c r="B124" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C124" s="44" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D124" s="44" t="str">
+        <x:v>px</x:v>
+      </x:c>
+      <x:c r="E124" s="44" t="str">
+        <x:v>지형 파괴 반경</x:v>
+      </x:c>
+      <x:c r="F124" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="26" customHeight="1">
+      <x:c r="A125" s="44" t="str">
+        <x:v>skill.revolver.2.max_damage</x:v>
+      </x:c>
+      <x:c r="B125" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C125" s="44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D125" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E125" s="44" t="str">
+        <x:v>최대 피해</x:v>
+      </x:c>
+      <x:c r="F125" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="26" customHeight="1">
+      <x:c r="A126" s="44" t="str">
+        <x:v>skill.revolver.2.healing</x:v>
+      </x:c>
+      <x:c r="B126" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C126" s="44" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D126" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E126" s="44" t="str">
+        <x:v>모든 진영 회복량</x:v>
+      </x:c>
+      <x:c r="F126" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="26" customHeight="1">
+      <x:c r="A127" s="44" t="str">
+        <x:v>skill.revolver.2.radius</x:v>
+      </x:c>
+      <x:c r="B127" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C127" s="44" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D127" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E127" s="44" t="str">
+        <x:v>효과 반경</x:v>
+      </x:c>
+      <x:c r="F127" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="26" customHeight="1">
+      <x:c r="A128" s="44" t="str">
+        <x:v>skill.revolver.2.cooldown</x:v>
+      </x:c>
+      <x:c r="B128" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C128" s="44" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D128" s="44" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E128" s="44" t="str">
+        <x:v>재사용 대기</x:v>
+      </x:c>
+      <x:c r="F128" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="26" customHeight="1">
+      <x:c r="A129" s="44" t="str">
+        <x:v>skill.revolver.2.force</x:v>
+      </x:c>
+      <x:c r="B129" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C129" s="44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D129" s="44" t="str">
+        <x:v>힘</x:v>
+      </x:c>
+      <x:c r="E129" s="44" t="str">
+        <x:v>자석 이동 힘</x:v>
+      </x:c>
+      <x:c r="F129" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="26" customHeight="1">
+      <x:c r="A130" s="44" t="str">
+        <x:v>skill.revolver.3.max_damage</x:v>
+      </x:c>
+      <x:c r="B130" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C130" s="44" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D130" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E130" s="44" t="str">
+        <x:v>최대 피해</x:v>
+      </x:c>
+      <x:c r="F130" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="26" customHeight="1">
+      <x:c r="A131" s="44" t="str">
+        <x:v>skill.revolver.3.radius</x:v>
+      </x:c>
+      <x:c r="B131" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C131" s="44" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="D131" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E131" s="44" t="str">
+        <x:v>효과 반경</x:v>
+      </x:c>
+      <x:c r="F131" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="26" customHeight="1">
+      <x:c r="A132" s="44" t="str">
+        <x:v>skill.revolver.3.count</x:v>
+      </x:c>
+      <x:c r="B132" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C132" s="44" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D132" s="44" t="str">
+        <x:v>개</x:v>
+      </x:c>
+      <x:c r="E132" s="44" t="str">
+        <x:v>공습 폭탄 수</x:v>
+      </x:c>
+      <x:c r="F132" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="26" customHeight="1">
+      <x:c r="A133" s="44" t="str">
+        <x:v>skill.revolver.3.spacing</x:v>
+      </x:c>
+      <x:c r="B133" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C133" s="44" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="D133" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E133" s="44" t="str">
+        <x:v>공습 간격</x:v>
+      </x:c>
+      <x:c r="F133" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="26" customHeight="1">
+      <x:c r="A134" s="44" t="str">
+        <x:v>skill.revolver.3.delay</x:v>
+      </x:c>
+      <x:c r="B134" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C134" s="44" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="D134" s="44" t="str">
+        <x:v>초</x:v>
+      </x:c>
+      <x:c r="E134" s="44" t="str">
+        <x:v>발동 대기</x:v>
+      </x:c>
+      <x:c r="F134" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="26" customHeight="1">
+      <x:c r="A135" s="44" t="str">
+        <x:v>skill.revolver.3.cooldown</x:v>
+      </x:c>
+      <x:c r="B135" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C135" s="44" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D135" s="44" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E135" s="44" t="str">
+        <x:v>재사용 대기</x:v>
+      </x:c>
+      <x:c r="F135" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="26" customHeight="1">
+      <x:c r="A136" s="44" t="str">
+        <x:v>skill.revolver.3.terrain_radius_px</x:v>
+      </x:c>
+      <x:c r="B136" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C136" s="44" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D136" s="44" t="str">
+        <x:v>px</x:v>
+      </x:c>
+      <x:c r="E136" s="44" t="str">
+        <x:v>지형 파괴 반경</x:v>
+      </x:c>
+      <x:c r="F136" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="26" customHeight="1">
+      <x:c r="A137" s="44" t="str">
+        <x:v>skill.magnet.1.max_damage</x:v>
+      </x:c>
+      <x:c r="B137" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C137" s="44" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D137" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E137" s="44" t="str">
+        <x:v>최대 피해</x:v>
+      </x:c>
+      <x:c r="F137" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="26" customHeight="1">
+      <x:c r="A138" s="44" t="str">
+        <x:v>skill.magnet.1.radius</x:v>
+      </x:c>
+      <x:c r="B138" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C138" s="44" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D138" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E138" s="44" t="str">
+        <x:v>효과 반경</x:v>
+      </x:c>
+      <x:c r="F138" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="26" customHeight="1">
+      <x:c r="A139" s="44" t="str">
+        <x:v>skill.magnet.1.force</x:v>
+      </x:c>
+      <x:c r="B139" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C139" s="44" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D139" s="44" t="str">
+        <x:v>힘</x:v>
+      </x:c>
+      <x:c r="E139" s="44" t="str">
+        <x:v>자석 이동 힘</x:v>
+      </x:c>
+      <x:c r="F139" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="26" customHeight="1">
+      <x:c r="A140" s="44" t="str">
+        <x:v>skill.magnet.1.cooldown</x:v>
+      </x:c>
+      <x:c r="B140" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C140" s="44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D140" s="44" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E140" s="44" t="str">
+        <x:v>재사용 대기</x:v>
+      </x:c>
+      <x:c r="F140" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="26" customHeight="1">
+      <x:c r="A141" s="44" t="str">
+        <x:v>skill.magnet.2.max_damage</x:v>
+      </x:c>
+      <x:c r="B141" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C141" s="44" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D141" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E141" s="44" t="str">
+        <x:v>최대 피해</x:v>
+      </x:c>
+      <x:c r="F141" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="26" customHeight="1">
+      <x:c r="A142" s="44" t="str">
+        <x:v>skill.magnet.2.radius</x:v>
+      </x:c>
+      <x:c r="B142" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C142" s="44" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D142" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E142" s="44" t="str">
+        <x:v>효과 반경</x:v>
+      </x:c>
+      <x:c r="F142" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="26" customHeight="1">
+      <x:c r="A143" s="44" t="str">
+        <x:v>skill.magnet.2.force</x:v>
+      </x:c>
+      <x:c r="B143" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C143" s="44" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D143" s="44" t="str">
+        <x:v>힘</x:v>
+      </x:c>
+      <x:c r="E143" s="44" t="str">
+        <x:v>자석 이동 힘</x:v>
+      </x:c>
+      <x:c r="F143" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="26" customHeight="1">
+      <x:c r="A144" s="44" t="str">
+        <x:v>skill.magnet.2.cooldown</x:v>
+      </x:c>
+      <x:c r="B144" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C144" s="44" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D144" s="44" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E144" s="44" t="str">
+        <x:v>재사용 대기</x:v>
+      </x:c>
+      <x:c r="F144" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="26" customHeight="1">
+      <x:c r="A145" s="44" t="str">
+        <x:v>skill.magnet.3.max_damage</x:v>
+      </x:c>
+      <x:c r="B145" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C145" s="44" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D145" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E145" s="44" t="str">
+        <x:v>최대 피해</x:v>
+      </x:c>
+      <x:c r="F145" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="26" customHeight="1">
+      <x:c r="A146" s="44" t="str">
+        <x:v>skill.magnet.3.radius</x:v>
+      </x:c>
+      <x:c r="B146" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C146" s="44" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D146" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E146" s="44" t="str">
+        <x:v>효과 반경</x:v>
+      </x:c>
+      <x:c r="F146" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="26" customHeight="1">
+      <x:c r="A147" s="44" t="str">
+        <x:v>skill.magnet.3.force</x:v>
+      </x:c>
+      <x:c r="B147" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C147" s="44" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D147" s="44" t="str">
+        <x:v>힘</x:v>
+      </x:c>
+      <x:c r="E147" s="44" t="str">
+        <x:v>자석 이동 힘</x:v>
+      </x:c>
+      <x:c r="F147" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="26" customHeight="1">
+      <x:c r="A148" s="44" t="str">
+        <x:v>skill.magnet.3.cooldown</x:v>
+      </x:c>
+      <x:c r="B148" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C148" s="44" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D148" s="44" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E148" s="44" t="str">
+        <x:v>재사용 대기</x:v>
+      </x:c>
+      <x:c r="F148" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="26" customHeight="1">
+      <x:c r="A149" s="44" t="str">
+        <x:v>skill.kettle.1.max_damage</x:v>
+      </x:c>
+      <x:c r="B149" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C149" s="44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D149" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E149" s="44" t="str">
+        <x:v>최대 피해</x:v>
+      </x:c>
+      <x:c r="F149" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="26" customHeight="1">
+      <x:c r="A150" s="44" t="str">
+        <x:v>skill.kettle.1.healing</x:v>
+      </x:c>
+      <x:c r="B150" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C150" s="44" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D150" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E150" s="44" t="str">
+        <x:v>모든 진영 회복량</x:v>
+      </x:c>
+      <x:c r="F150" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="26" customHeight="1">
+      <x:c r="A151" s="44" t="str">
+        <x:v>skill.kettle.1.radius</x:v>
+      </x:c>
+      <x:c r="B151" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C151" s="44" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="D151" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E151" s="44" t="str">
+        <x:v>효과 반경</x:v>
+      </x:c>
+      <x:c r="F151" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="26" customHeight="1">
+      <x:c r="A152" s="44" t="str">
+        <x:v>skill.kettle.1.force</x:v>
+      </x:c>
+      <x:c r="B152" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C152" s="44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D152" s="44" t="str">
+        <x:v>힘</x:v>
+      </x:c>
+      <x:c r="E152" s="44" t="str">
+        <x:v>자석 이동 힘</x:v>
+      </x:c>
+      <x:c r="F152" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="26" customHeight="1">
+      <x:c r="A153" s="44" t="str">
+        <x:v>skill.kettle.1.cooldown</x:v>
+      </x:c>
+      <x:c r="B153" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C153" s="44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D153" s="44" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E153" s="44" t="str">
+        <x:v>재사용 대기</x:v>
+      </x:c>
+      <x:c r="F153" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="26" customHeight="1">
+      <x:c r="A154" s="44" t="str">
+        <x:v>skill.kettle.2.max_damage</x:v>
+      </x:c>
+      <x:c r="B154" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C154" s="44" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D154" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E154" s="44" t="str">
+        <x:v>최대 피해</x:v>
+      </x:c>
+      <x:c r="F154" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="26" customHeight="1">
+      <x:c r="A155" s="44" t="str">
+        <x:v>skill.kettle.2.radius</x:v>
+      </x:c>
+      <x:c r="B155" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C155" s="44" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="D155" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E155" s="44" t="str">
+        <x:v>효과 반경</x:v>
+      </x:c>
+      <x:c r="F155" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="26" customHeight="1">
+      <x:c r="A156" s="44" t="str">
+        <x:v>skill.kettle.2.zone_damage</x:v>
+      </x:c>
+      <x:c r="B156" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C156" s="44" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D156" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E156" s="44" t="str">
+        <x:v>장판 턴 피해</x:v>
+      </x:c>
+      <x:c r="F156" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="26" customHeight="1">
+      <x:c r="A157" s="44" t="str">
+        <x:v>skill.kettle.2.zone_rounds</x:v>
+      </x:c>
+      <x:c r="B157" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C157" s="44" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D157" s="44" t="str">
+        <x:v>라운드</x:v>
+      </x:c>
+      <x:c r="E157" s="44" t="str">
+        <x:v>장판 지속</x:v>
+      </x:c>
+      <x:c r="F157" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="26" customHeight="1">
+      <x:c r="A158" s="44" t="str">
+        <x:v>skill.kettle.2.zone_length</x:v>
+      </x:c>
+      <x:c r="B158" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C158" s="44" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D158" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E158" s="44" t="str">
+        <x:v>장판 길이</x:v>
+      </x:c>
+      <x:c r="F158" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="26" customHeight="1">
+      <x:c r="A159" s="44" t="str">
+        <x:v>skill.kettle.2.slow</x:v>
+      </x:c>
+      <x:c r="B159" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C159" s="44" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="D159" s="44" t="str">
+        <x:v>배율</x:v>
+      </x:c>
+      <x:c r="E159" s="44" t="str">
+        <x:v>장판 이동속도</x:v>
+      </x:c>
+      <x:c r="F159" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="26" customHeight="1">
+      <x:c r="A160" s="44" t="str">
+        <x:v>skill.kettle.2.cooldown</x:v>
+      </x:c>
+      <x:c r="B160" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C160" s="44" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D160" s="44" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E160" s="44" t="str">
+        <x:v>재사용 대기</x:v>
+      </x:c>
+      <x:c r="F160" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="26" customHeight="1">
+      <x:c r="A161" s="44" t="str">
+        <x:v>skill.kettle.3.max_damage</x:v>
+      </x:c>
+      <x:c r="B161" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C161" s="44" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D161" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E161" s="44" t="str">
+        <x:v>최대 피해</x:v>
+      </x:c>
+      <x:c r="F161" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="26" customHeight="1">
+      <x:c r="A162" s="44" t="str">
+        <x:v>skill.kettle.3.radius</x:v>
+      </x:c>
+      <x:c r="B162" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C162" s="44" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="D162" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E162" s="44" t="str">
+        <x:v>효과 반경</x:v>
+      </x:c>
+      <x:c r="F162" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="26" customHeight="1">
+      <x:c r="A163" s="44" t="str">
+        <x:v>skill.kettle.3.delay</x:v>
+      </x:c>
+      <x:c r="B163" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C163" s="44" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="D163" s="44" t="str">
+        <x:v>초</x:v>
+      </x:c>
+      <x:c r="E163" s="44" t="str">
+        <x:v>발동 대기</x:v>
+      </x:c>
+      <x:c r="F163" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="26" customHeight="1">
+      <x:c r="A164" s="44" t="str">
+        <x:v>skill.kettle.3.terrain_radius_px</x:v>
+      </x:c>
+      <x:c r="B164" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C164" s="44" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D164" s="44" t="str">
+        <x:v>px</x:v>
+      </x:c>
+      <x:c r="E164" s="44" t="str">
+        <x:v>지형 파괴 반경</x:v>
+      </x:c>
+      <x:c r="F164" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="26" customHeight="1">
+      <x:c r="A165" s="44" t="str">
+        <x:v>skill.kettle.3.cooldown</x:v>
+      </x:c>
+      <x:c r="B165" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C165" s="44" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D165" s="44" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E165" s="44" t="str">
+        <x:v>재사용 대기</x:v>
+      </x:c>
+      <x:c r="F165" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="26" customHeight="1">
+      <x:c r="A166" s="44" t="str">
+        <x:v>common.potion.healing</x:v>
+      </x:c>
+      <x:c r="B166" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C166" s="44" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D166" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E166" s="44" t="str">
+        <x:v>포션 모든 진영 치유</x:v>
+      </x:c>
+      <x:c r="F166" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="26" customHeight="1">
+      <x:c r="A167" s="44" t="str">
+        <x:v>common.potion.radius</x:v>
+      </x:c>
+      <x:c r="B167" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C167" s="44" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="D167" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E167" s="44" t="str">
+        <x:v>포션 치유 반경</x:v>
+      </x:c>
+      <x:c r="F167" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="26" customHeight="1">
+      <x:c r="A168" s="44" t="str">
+        <x:v>common.ice.zone_length</x:v>
+      </x:c>
+      <x:c r="B168" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C168" s="44" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="D168" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E168" s="44" t="str">
+        <x:v>얼음 장판 길이</x:v>
+      </x:c>
+      <x:c r="F168" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="26" customHeight="1">
+      <x:c r="A169" s="44" t="str">
+        <x:v>common.ice.zone_rounds</x:v>
+      </x:c>
+      <x:c r="B169" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C169" s="44" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D169" s="44" t="str">
+        <x:v>라운드</x:v>
+      </x:c>
+      <x:c r="E169" s="44" t="str">
+        <x:v>얼음 장판 지속</x:v>
+      </x:c>
+      <x:c r="F169" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="26" customHeight="1">
+      <x:c r="A170" s="44" t="str">
+        <x:v>common.ice.slow</x:v>
+      </x:c>
+      <x:c r="B170" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C170" s="44" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="D170" s="44" t="str">
+        <x:v>배율</x:v>
+      </x:c>
+      <x:c r="E170" s="44" t="str">
+        <x:v>얼음 장판 이동속도</x:v>
+      </x:c>
+      <x:c r="F170" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="26" customHeight="1">
+      <x:c r="A171" s="44" t="str">
+        <x:v>common.smoke.radius</x:v>
+      </x:c>
+      <x:c r="B171" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C171" s="44" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="D171" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E171" s="44" t="str">
+        <x:v>연막 조준 방해 범위</x:v>
+      </x:c>
+      <x:c r="F171" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="26" customHeight="1">
+      <x:c r="A172" s="44" t="str">
+        <x:v>common.smoke.zone_rounds</x:v>
+      </x:c>
+      <x:c r="B172" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C172" s="44" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D172" s="44" t="str">
+        <x:v>라운드</x:v>
+      </x:c>
+      <x:c r="E172" s="44" t="str">
+        <x:v>연막 지속</x:v>
+      </x:c>
+      <x:c r="F172" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="26" customHeight="1">
+      <x:c r="A173" s="44" t="str">
+        <x:v>common.helmet.absorption</x:v>
+      </x:c>
+      <x:c r="B173" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C173" s="44" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D173" s="44" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E173" s="44" t="str">
+        <x:v>다음 피해 한 번 흡수</x:v>
+      </x:c>
+      <x:c r="F173" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="26" customHeight="1">
+      <x:c r="A174" s="44" t="str">
+        <x:v>training.turn_seconds</x:v>
+      </x:c>
+      <x:c r="B174" s="44" t="str">
+        <x:v>추가 캐릭터</x:v>
+      </x:c>
+      <x:c r="C174" s="44" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="D174" s="44" t="str">
+        <x:v>초</x:v>
+      </x:c>
+      <x:c r="E174" s="44" t="str">
+        <x:v>훈련장 행동 시간</x:v>
+      </x:c>
+      <x:c r="F174" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
@@ -4469,7 +6351,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d3aedd762984575"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ab31e6e87df4123"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/Assets/GameData/ObjectHeadData.xlsx
+++ b/Assets/GameData/ObjectHeadData.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="번역" sheetId="1" r:id="R66f70e607fd04cd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수치" sheetId="2" r:id="Rfc528d129e054c7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계산기" sheetId="3" r:id="R29069b44b8594611"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="번역" sheetId="1" r:id="Rf85516674c094251"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수치" sheetId="2" r:id="R71b5bfb0c1664916"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계산기" sheetId="3" r:id="R3e02c9bdd81e49f6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -197,7 +197,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="47">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -300,6 +300,9 @@
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -308,7 +311,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LocalizationTable" displayName="LocalizationTable" ref="A4:D168" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LocalizationTable" displayName="LocalizationTable" ref="A4:D177" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="key"/>
     <x:tableColumn id="2" name="한국어"/>
@@ -2881,6 +2884,134 @@
         <x:v>0916 확장</x:v>
       </x:c>
     </x:row>
+    <x:row r="169" ht="46" customHeight="1">
+      <x:c r="A169" s="46" t="str">
+        <x:v>rooms_refresh</x:v>
+      </x:c>
+      <x:c r="B169" s="46" t="str">
+        <x:v>새로고침</x:v>
+      </x:c>
+      <x:c r="C169" s="46" t="str">
+        <x:v>Refresh</x:v>
+      </x:c>
+      <x:c r="D169" s="46" t="str">
+        <x:v>방 목록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="46" customHeight="1">
+      <x:c r="A170" s="46" t="str">
+        <x:v>rooms_loading</x:v>
+      </x:c>
+      <x:c r="B170" s="46" t="str">
+        <x:v>참가할 수 있는 방을 찾고 있어요…</x:v>
+      </x:c>
+      <x:c r="C170" s="46" t="str">
+        <x:v>Looking for available rooms…</x:v>
+      </x:c>
+      <x:c r="D170" s="46" t="str">
+        <x:v>방 목록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="46" customHeight="1">
+      <x:c r="A171" s="46" t="str">
+        <x:v>rooms_empty</x:v>
+      </x:c>
+      <x:c r="B171" s="46" t="str">
+        <x:v>열려 있는 방이 없어요. 방을 만들거나 코드를 입력하세요.</x:v>
+      </x:c>
+      <x:c r="C171" s="46" t="str">
+        <x:v>No open rooms. Create a room or enter a code.</x:v>
+      </x:c>
+      <x:c r="D171" s="46" t="str">
+        <x:v>방 목록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="46" customHeight="1">
+      <x:c r="A172" s="46" t="str">
+        <x:v>rooms_failed</x:v>
+      </x:c>
+      <x:c r="B172" s="46" t="str">
+        <x:v>방 목록을 불러오지 못했어요. 연결을 확인하고 다시 시도하세요.</x:v>
+      </x:c>
+      <x:c r="C172" s="46" t="str">
+        <x:v>Could not load rooms. Check your connection and retry.</x:v>
+      </x:c>
+      <x:c r="D172" s="46" t="str">
+        <x:v>방 목록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="46" customHeight="1">
+      <x:c r="A173" s="46" t="str">
+        <x:v>rooms_legacy</x:v>
+      </x:c>
+      <x:c r="B173" s="46" t="str">
+        <x:v>현재 연결에서는 코드로 참가하세요.</x:v>
+      </x:c>
+      <x:c r="C173" s="46" t="str">
+        <x:v>Join by code on this connection.</x:v>
+      </x:c>
+      <x:c r="D173" s="46" t="str">
+        <x:v>방 목록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="46" customHeight="1">
+      <x:c r="A174" s="46" t="str">
+        <x:v>rooms_row</x:v>
+      </x:c>
+      <x:c r="B174" s="46" t="str">
+        <x:v>{0}  ·  {1}/{2}명
+{3}  ·  {4}</x:v>
+      </x:c>
+      <x:c r="C174" s="46" t="str">
+        <x:v>{0}  ·  {1}/{2} players
+{3}  ·  {4}</x:v>
+      </x:c>
+      <x:c r="D174" s="46" t="str">
+        <x:v>방 목록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="46" customHeight="1">
+      <x:c r="A175" s="46" t="str">
+        <x:v>rooms_join_failed</x:v>
+      </x:c>
+      <x:c r="B175" s="46" t="str">
+        <x:v>방이 가득 찼거나 이미 시작됐어요. 새로고침 후 다시 선택하세요.</x:v>
+      </x:c>
+      <x:c r="C175" s="46" t="str">
+        <x:v>The room is full or has started. Refresh and choose another room.</x:v>
+      </x:c>
+      <x:c r="D175" s="46" t="str">
+        <x:v>방 목록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="46" customHeight="1">
+      <x:c r="A176" s="46" t="str">
+        <x:v>rooms_joining</x:v>
+      </x:c>
+      <x:c r="B176" s="46" t="str">
+        <x:v>방에 참가하고 있어요…</x:v>
+      </x:c>
+      <x:c r="C176" s="46" t="str">
+        <x:v>Joining room…</x:v>
+      </x:c>
+      <x:c r="D176" s="46" t="str">
+        <x:v>방 목록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="46" customHeight="1">
+      <x:c r="A177" s="46" t="str">
+        <x:v>rooms_count</x:v>
+      </x:c>
+      <x:c r="B177" s="46" t="str">
+        <x:v>참가 가능한 방 {0}개</x:v>
+      </x:c>
+      <x:c r="C177" s="46" t="str">
+        <x:v>{0} available rooms</x:v>
+      </x:c>
+      <x:c r="D177" s="46" t="str">
+        <x:v>방 목록</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
@@ -2888,7 +3019,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb404f63f469f4691"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ffd7d9c488b40d4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6351,7 +6482,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ab31e6e87df4123"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57617daa4663401e"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/Assets/GameData/ObjectHeadData.xlsx
+++ b/Assets/GameData/ObjectHeadData.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="번역" sheetId="1" r:id="Rf85516674c094251"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수치" sheetId="2" r:id="R71b5bfb0c1664916"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계산기" sheetId="3" r:id="R3e02c9bdd81e49f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="번역" sheetId="1" r:id="R1bd95f3d232247ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수치" sheetId="2" r:id="R1fc335db61e5449a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계산기" sheetId="3" r:id="R3a22f4ea35a242b5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -311,7 +311,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LocalizationTable" displayName="LocalizationTable" ref="A4:D177" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LocalizationTable" displayName="LocalizationTable" ref="A4:D246" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="key"/>
     <x:tableColumn id="2" name="한국어"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="BalanceTable" displayName="BalanceTable" ref="A4:F174" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="BalanceTable" displayName="BalanceTable" ref="A4:F217" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="key"/>
     <x:tableColumn id="2" name="분류"/>
@@ -1447,13 +1447,13 @@
         <x:v>local_play</x:v>
       </x:c>
       <x:c r="B67" s="45" t="str">
-        <x:v>한 PC에서 플레이</x:v>
+        <x:v>AI 대전</x:v>
       </x:c>
       <x:c r="C67" s="45" t="str">
-        <x:v>PLAY ON ONE PC</x:v>
+        <x:v>AI BATTLE</x:v>
       </x:c>
       <x:c r="D67" s="45" t="str">
-        <x:v>0916</x:v>
+        <x:v>로컬 AI 전투 진입</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="52" customHeight="1">
@@ -1461,13 +1461,13 @@
         <x:v>local_title</x:v>
       </x:c>
       <x:c r="B68" s="45" t="str">
-        <x:v>로컬 대전 · 팀 편성</x:v>
+        <x:v>AI 대전 · 팀 편성</x:v>
       </x:c>
       <x:c r="C68" s="45" t="str">
-        <x:v>LOCAL MATCH · SQUAD SELECT</x:v>
+        <x:v>AI BATTLE · SQUAD SELECT</x:v>
       </x:c>
       <x:c r="D68" s="45" t="str">
-        <x:v>0916</x:v>
+        <x:v>로컬 AI 전투</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="52" customHeight="1">
@@ -1475,13 +1475,13 @@
         <x:v>local_shared_screen</x:v>
       </x:c>
       <x:c r="B69" s="45" t="str">
-        <x:v>같은 화면에서 번갈아 플레이합니다</x:v>
+        <x:v>서버 없이 컴퓨터 상대와 오프라인으로 플레이합니다.</x:v>
       </x:c>
       <x:c r="C69" s="45" t="str">
-        <x:v>SHARED SCREEN · TAKE TURNS</x:v>
+        <x:v>Play offline against computer-controlled opponents.</x:v>
       </x:c>
       <x:c r="D69" s="45" t="str">
-        <x:v>0916</x:v>
+        <x:v>로컬 AI 전투</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="52" customHeight="1">
@@ -1503,13 +1503,13 @@
         <x:v>confirm_team</x:v>
       </x:c>
       <x:c r="B71" s="45" t="str">
-        <x:v>팀 확정 / 다음 플레이어</x:v>
+        <x:v>팀 확정</x:v>
       </x:c>
       <x:c r="C71" s="45" t="str">
-        <x:v>CONFIRM SQUAD / NEXT PLAYER</x:v>
+        <x:v>CONFIRM SQUAD</x:v>
       </x:c>
       <x:c r="D71" s="45" t="str">
-        <x:v>0916</x:v>
+        <x:v>공용 선택 버튼</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="52" customHeight="1">
@@ -1657,10 +1657,10 @@
         <x:v>map_meadow</x:v>
       </x:c>
       <x:c r="B81" s="45" t="str">
-        <x:v>바람 초원</x:v>
+        <x:v>외딴 등대 섬</x:v>
       </x:c>
       <x:c r="C81" s="45" t="str">
-        <x:v>WIND MEADOW</x:v>
+        <x:v>Lonely Lighthouse</x:v>
       </x:c>
       <x:c r="D81" s="45" t="str">
         <x:v>0916</x:v>
@@ -1671,10 +1671,10 @@
         <x:v>map_meadow_desc</x:v>
       </x:c>
       <x:c r="B82" s="45" t="str">
-        <x:v>동일 높이의 시작 발판과 완만한 엄폐 언덕</x:v>
+        <x:v>높은 등대와 계단 절벽. 아래 동굴로 우회할 수 있습니다.</x:v>
       </x:c>
       <x:c r="C82" s="45" t="str">
-        <x:v>Equal-height spawns with gentle cover slopes</x:v>
+        <x:v>Tall lighthouse and stepped cliffs with a lower cave route.</x:v>
       </x:c>
       <x:c r="D82" s="45" t="str">
         <x:v>0916</x:v>
@@ -1685,10 +1685,10 @@
         <x:v>map_citadel</x:v>
       </x:c>
       <x:c r="B83" s="45" t="str">
-        <x:v>쌍둥이 성채</x:v>
+        <x:v>무너진 항구</x:v>
       </x:c>
       <x:c r="C83" s="45" t="str">
-        <x:v>TWIN CITADELS</x:v>
+        <x:v>Ruined Harbor</x:v>
       </x:c>
       <x:c r="D83" s="45" t="str">
         <x:v>0916</x:v>
@@ -1699,13 +1699,13 @@
         <x:v>map_citadel_desc</x:v>
       </x:c>
       <x:c r="B84" s="45" t="str">
-        <x:v>동일한 방어 발판, 파괴 가능한 아치와 지하 공간</x:v>
+        <x:v>항구 절벽과 지붕 위에서 싸우거나 관통 동굴로 우회하세요.</x:v>
       </x:c>
       <x:c r="C84" s="45" t="str">
-        <x:v>Equal defensive platforms, breakable arches and cavities</x:v>
+        <x:v>Fight over harbor cliffs and roofs or take the through-cave route.</x:v>
       </x:c>
       <x:c r="D84" s="45" t="str">
-        <x:v>0916</x:v>
+        <x:v>맵 설명</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="52" customHeight="1">
@@ -1713,10 +1713,10 @@
         <x:v>map_reef</x:v>
       </x:c>
       <x:c r="B85" s="45" t="str">
-        <x:v>조각섬 군도</x:v>
+        <x:v>난파선 해안</x:v>
       </x:c>
       <x:c r="C85" s="45" t="str">
-        <x:v>SHATTERED REEF</x:v>
+        <x:v>Shipwreck Coast</x:v>
       </x:c>
       <x:c r="D85" s="45" t="str">
         <x:v>0916</x:v>
@@ -1727,10 +1727,10 @@
         <x:v>map_reef_desc</x:v>
       </x:c>
       <x:c r="B86" s="45" t="str">
-        <x:v>네 개의 동일 높이 섬과 좁은 도약 구간</x:v>
+        <x:v>갈라진 해안 위 난파선. 아래 통로와 갑판의 고저차를 활용하세요.</x:v>
       </x:c>
       <x:c r="C86" s="45" t="str">
-        <x:v>Four equal-height islands with narrow jump gaps</x:v>
+        <x:v>Shipwrecks above a split coast with decks and lower passages.</x:v>
       </x:c>
       <x:c r="D86" s="45" t="str">
         <x:v>0916</x:v>
@@ -3010,6 +3010,972 @@
       </x:c>
       <x:c r="D177" s="46" t="str">
         <x:v>방 목록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="64" customHeight="1">
+      <x:c r="A178" s="46" t="str">
+        <x:v>common_lock</x:v>
+      </x:c>
+      <x:c r="B178" s="46" t="str">
+        <x:v>자물쇠</x:v>
+      </x:c>
+      <x:c r="C178" s="46" t="str">
+        <x:v>Padlock</x:v>
+      </x:c>
+      <x:c r="D178" s="46" t="str">
+        <x:v>공용 머리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="142" customHeight="1">
+      <x:c r="A179" s="46" t="str">
+        <x:v>common_lock_description</x:v>
+      </x:c>
+      <x:c r="B179" s="46" t="str">
+        <x:v>좁은 범위의 모든 진영을 포획합니다. 2라운드 동안 해당 캐릭터의 차례를 건너뛰고 라운드마다 봉인 피해를 받습니다. 외부 피해와 넉백에는 면역이며, 재포획으로 연장되지 않습니다.</x:v>
+      </x:c>
+      <x:c r="C179" s="46" t="str">
+        <x:v>Captures any faction in a small area. For 2 rounds, captives skip their turn and take captivity damage each round, while resisting external damage and knockback. Recapture does not extend the effect.</x:v>
+      </x:c>
+      <x:c r="D179" s="46" t="str">
+        <x:v>지속·피해는 수치 시트</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="64" customHeight="1">
+      <x:c r="A180" s="46" t="str">
+        <x:v>status_captured</x:v>
+      </x:c>
+      <x:c r="B180" s="46" t="str">
+        <x:v>봉인 · 남은 라운드 {0}</x:v>
+      </x:c>
+      <x:c r="C180" s="46" t="str">
+        <x:v>Captured · {0} rounds remaining</x:v>
+      </x:c>
+      <x:c r="D180" s="46" t="str">
+        <x:v>전투 상태</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="64" customHeight="1">
+      <x:c r="A181" s="46" t="str">
+        <x:v>room_public</x:v>
+      </x:c>
+      <x:c r="B181" s="46" t="str">
+        <x:v>공개방 · 누구나 참가</x:v>
+      </x:c>
+      <x:c r="C181" s="46" t="str">
+        <x:v>Public · open to everyone</x:v>
+      </x:c>
+      <x:c r="D181" s="46" t="str">
+        <x:v>방 공개 설정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="64" customHeight="1">
+      <x:c r="A182" s="46" t="str">
+        <x:v>room_private</x:v>
+      </x:c>
+      <x:c r="B182" s="46" t="str">
+        <x:v>비밀방 · 코드 + 비밀번호</x:v>
+      </x:c>
+      <x:c r="C182" s="46" t="str">
+        <x:v>Private · code + password</x:v>
+      </x:c>
+      <x:c r="D182" s="46" t="str">
+        <x:v>방 공개 설정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="64" customHeight="1">
+      <x:c r="A183" s="46" t="str">
+        <x:v>room_password_hint</x:v>
+      </x:c>
+      <x:c r="B183" s="46" t="str">
+        <x:v>비밀번호 (4~32자, 영문·숫자·기호)</x:v>
+      </x:c>
+      <x:c r="C183" s="46" t="str">
+        <x:v>Password (4–32 ASCII characters)</x:v>
+      </x:c>
+      <x:c r="D183" s="46" t="str">
+        <x:v>공백 제외</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="64" customHeight="1">
+      <x:c r="A184" s="46" t="str">
+        <x:v>room_join_password</x:v>
+      </x:c>
+      <x:c r="B184" s="46" t="str">
+        <x:v>비밀방 비밀번호 (공개방은 비워두세요)</x:v>
+      </x:c>
+      <x:c r="C184" s="46" t="str">
+        <x:v>Private room password (leave blank for public)</x:v>
+      </x:c>
+      <x:c r="D184" s="46" t="str">
+        <x:v>참가 입력</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="64" customHeight="1">
+      <x:c r="A185" s="46" t="str">
+        <x:v>room_private_notice</x:v>
+      </x:c>
+      <x:c r="B185" s="46" t="str">
+        <x:v>비밀방은 방 목록과 빠른 매칭에 나오지 않습니다.</x:v>
+      </x:c>
+      <x:c r="C185" s="46" t="str">
+        <x:v>Private rooms never appear in browsing or quick matching.</x:v>
+      </x:c>
+      <x:c r="D185" s="46" t="str">
+        <x:v>방 생성 설명</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="64" customHeight="1">
+      <x:c r="A186" s="46" t="str">
+        <x:v>room_password_required</x:v>
+      </x:c>
+      <x:c r="B186" s="46" t="str">
+        <x:v>비밀방이에요. 방장에게 받은 비밀번호를 입력하세요.</x:v>
+      </x:c>
+      <x:c r="C186" s="46" t="str">
+        <x:v>Enter the private room password from the host.</x:v>
+      </x:c>
+      <x:c r="D186" s="46" t="str">
+        <x:v>오류</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="64" customHeight="1">
+      <x:c r="A187" s="46" t="str">
+        <x:v>room_password_incorrect</x:v>
+      </x:c>
+      <x:c r="B187" s="46" t="str">
+        <x:v>비밀번호가 맞지 않아요. 다시 확인해 주세요.</x:v>
+      </x:c>
+      <x:c r="C187" s="46" t="str">
+        <x:v>Incorrect password. Please try again.</x:v>
+      </x:c>
+      <x:c r="D187" s="46" t="str">
+        <x:v>오류</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="64" customHeight="1">
+      <x:c r="A188" s="46" t="str">
+        <x:v>room_password_invalid</x:v>
+      </x:c>
+      <x:c r="B188" s="46" t="str">
+        <x:v>비밀번호는 공백 없이 영문·숫자·기호 4~32자로 설정하세요.</x:v>
+      </x:c>
+      <x:c r="C188" s="46" t="str">
+        <x:v>Use 4–32 ASCII letters, numbers or symbols, without spaces.</x:v>
+      </x:c>
+      <x:c r="D188" s="46" t="str">
+        <x:v>오류</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="64" customHeight="1">
+      <x:c r="A189" s="46" t="str">
+        <x:v>room_password_rate_limited</x:v>
+      </x:c>
+      <x:c r="B189" s="46" t="str">
+        <x:v>입력 횟수가 많아요. 1분 뒤 다시 시도해 주세요.</x:v>
+      </x:c>
+      <x:c r="C189" s="46" t="str">
+        <x:v>Too many attempts. Please retry in one minute.</x:v>
+      </x:c>
+      <x:c r="D189" s="46" t="str">
+        <x:v>오류</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="64" customHeight="1">
+      <x:c r="A190" s="46" t="str">
+        <x:v>private_requires_authority</x:v>
+      </x:c>
+      <x:c r="B190" s="46" t="str">
+        <x:v>비밀방은 전용 서버 연결에서 사용할 수 있어요.</x:v>
+      </x:c>
+      <x:c r="C190" s="46" t="str">
+        <x:v>Private rooms require the dedicated server connection.</x:v>
+      </x:c>
+      <x:c r="D190" s="46" t="str">
+        <x:v>오류</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="64" customHeight="1">
+      <x:c r="A191" s="46" t="str">
+        <x:v>incompatible_ruleset</x:v>
+      </x:c>
+      <x:c r="B191" s="46" t="str">
+        <x:v>게임 버전이 달라요. 같은 버전으로 실행해 주세요.</x:v>
+      </x:c>
+      <x:c r="C191" s="46" t="str">
+        <x:v>Game versions differ. Please update to the same version.</x:v>
+      </x:c>
+      <x:c r="D191" s="46" t="str">
+        <x:v>오류</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="64" customHeight="1">
+      <x:c r="A192" s="46" t="str">
+        <x:v>room_not_found</x:v>
+      </x:c>
+      <x:c r="B192" s="46" t="str">
+        <x:v>방을 찾을 수 없어요. 코드를 확인해 주세요.</x:v>
+      </x:c>
+      <x:c r="C192" s="46" t="str">
+        <x:v>Room not found. Please check the code.</x:v>
+      </x:c>
+      <x:c r="D192" s="46" t="str">
+        <x:v>오류</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="64" customHeight="1">
+      <x:c r="A193" s="46" t="str">
+        <x:v>room_full</x:v>
+      </x:c>
+      <x:c r="B193" s="46" t="str">
+        <x:v>방이 가득 찼어요.</x:v>
+      </x:c>
+      <x:c r="C193" s="46" t="str">
+        <x:v>The room is full.</x:v>
+      </x:c>
+      <x:c r="D193" s="46" t="str">
+        <x:v>오류</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="64" customHeight="1">
+      <x:c r="A194" s="46" t="str">
+        <x:v>ai_instructions</x:v>
+      </x:c>
+      <x:c r="B194" s="46" t="str">
+        <x:v>내 캐릭터를 선택한 뒤 게임을 시작하세요. 나머지 플레이어는 AI가 조작합니다.</x:v>
+      </x:c>
+      <x:c r="C194" s="46" t="str">
+        <x:v>Choose your squad, then start. The remaining players are controlled by AI.</x:v>
+      </x:c>
+      <x:c r="D194" s="46" t="str">
+        <x:v>로컬 AI 전투</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="64" customHeight="1">
+      <x:c r="A195" s="46" t="str">
+        <x:v>training_instructions</x:v>
+      </x:c>
+      <x:c r="B195" s="46" t="str">
+        <x:v>연습할 양쪽 팀을 선택한 뒤 훈련장을 시작하세요.</x:v>
+      </x:c>
+      <x:c r="C195" s="46" t="str">
+        <x:v>Choose both practice squads, then enter training.</x:v>
+      </x:c>
+      <x:c r="D195" s="46" t="str">
+        <x:v>훈련장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="64" customHeight="1">
+      <x:c r="A196" s="46" t="str">
+        <x:v>training_timer</x:v>
+      </x:c>
+      <x:c r="B196" s="46" t="str">
+        <x:v>타이머 정지/재개</x:v>
+      </x:c>
+      <x:c r="C196" s="46" t="str">
+        <x:v>PAUSE/RESUME TIMER</x:v>
+      </x:c>
+      <x:c r="D196" s="46" t="str">
+        <x:v>훈련장 도구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="64" customHeight="1">
+      <x:c r="A197" s="46" t="str">
+        <x:v>training_heal</x:v>
+      </x:c>
+      <x:c r="B197" s="46" t="str">
+        <x:v>전체 회복</x:v>
+      </x:c>
+      <x:c r="C197" s="46" t="str">
+        <x:v>HEAL ALL</x:v>
+      </x:c>
+      <x:c r="D197" s="46" t="str">
+        <x:v>훈련장 도구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="64" customHeight="1">
+      <x:c r="A198" s="46" t="str">
+        <x:v>training_skip</x:v>
+      </x:c>
+      <x:c r="B198" s="46" t="str">
+        <x:v>턴 넘기기</x:v>
+      </x:c>
+      <x:c r="C198" s="46" t="str">
+        <x:v>SKIP TURN</x:v>
+      </x:c>
+      <x:c r="D198" s="46" t="str">
+        <x:v>훈련장 도구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="64" customHeight="1">
+      <x:c r="A199" s="46" t="str">
+        <x:v>ai_roster_random</x:v>
+      </x:c>
+      <x:c r="B199" s="46" t="str">
+        <x:v>AI 편성 · 랜덤</x:v>
+      </x:c>
+      <x:c r="C199" s="46" t="str">
+        <x:v>AI ROSTER · RANDOM</x:v>
+      </x:c>
+      <x:c r="D199" s="46" t="str">
+        <x:v>AI 대전 설정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="64" customHeight="1">
+      <x:c r="A200" s="46" t="str">
+        <x:v>ai_roster_fixed</x:v>
+      </x:c>
+      <x:c r="B200" s="46" t="str">
+        <x:v>AI 편성 · 고정</x:v>
+      </x:c>
+      <x:c r="C200" s="46" t="str">
+        <x:v>AI ROSTER · FIXED</x:v>
+      </x:c>
+      <x:c r="D200" s="46" t="str">
+        <x:v>AI 대전 설정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="64" customHeight="1">
+      <x:c r="A201" s="46" t="str">
+        <x:v>ai_difficulty_beginner</x:v>
+      </x:c>
+      <x:c r="B201" s="46" t="str">
+        <x:v>AI 난이도 · 초보</x:v>
+      </x:c>
+      <x:c r="C201" s="46" t="str">
+        <x:v>AI DIFFICULTY · BEGINNER</x:v>
+      </x:c>
+      <x:c r="D201" s="46" t="str">
+        <x:v>AI 대전 설정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="64" customHeight="1">
+      <x:c r="A202" s="46" t="str">
+        <x:v>ai_difficulty_normal</x:v>
+      </x:c>
+      <x:c r="B202" s="46" t="str">
+        <x:v>AI 난이도 · 일반</x:v>
+      </x:c>
+      <x:c r="C202" s="46" t="str">
+        <x:v>AI DIFFICULTY · NORMAL</x:v>
+      </x:c>
+      <x:c r="D202" s="46" t="str">
+        <x:v>AI 대전 설정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="64" customHeight="1">
+      <x:c r="A203" s="46" t="str">
+        <x:v>ai_difficulty_pro</x:v>
+      </x:c>
+      <x:c r="B203" s="46" t="str">
+        <x:v>AI 난이도 · 프로</x:v>
+      </x:c>
+      <x:c r="C203" s="46" t="str">
+        <x:v>AI DIFFICULTY · PRO</x:v>
+      </x:c>
+      <x:c r="D203" s="46" t="str">
+        <x:v>AI 대전 설정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="64" customHeight="1">
+      <x:c r="A204" s="46" t="str">
+        <x:v>ai_roster_select</x:v>
+      </x:c>
+      <x:c r="B204" s="46" t="str">
+        <x:v>AI 편성 · 직접 선택</x:v>
+      </x:c>
+      <x:c r="C204" s="46" t="str">
+        <x:v>AI ROSTER · SELECT</x:v>
+      </x:c>
+      <x:c r="D204" s="46" t="str">
+        <x:v>AI 대전 설정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="64" customHeight="1">
+      <x:c r="A205" s="46" t="str">
+        <x:v>edit_local_squad</x:v>
+      </x:c>
+      <x:c r="B205" s="46" t="str">
+        <x:v>편성 대상: P{0}  ›</x:v>
+      </x:c>
+      <x:c r="C205" s="46" t="str">
+        <x:v>EDIT SQUAD: P{0}  ›</x:v>
+      </x:c>
+      <x:c r="D205" s="46" t="str">
+        <x:v>클릭하면 다음 플레이어의 캐릭터를 편성</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="58" customHeight="1">
+      <x:c r="A206" s="45" t="str">
+        <x:v>map_tidal_caverns</x:v>
+      </x:c>
+      <x:c r="B206" s="45" t="str">
+        <x:v>숨은 바닷길</x:v>
+      </x:c>
+      <x:c r="C206" s="45" t="str">
+        <x:v>Tidal Caverns</x:v>
+      </x:c>
+      <x:c r="D206" s="45" t="str">
+        <x:v>맵과 탈출 도구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="58" customHeight="1">
+      <x:c r="A207" s="45" t="str">
+        <x:v>map_tidal_caverns_description</x:v>
+      </x:c>
+      <x:c r="B207" s="45" t="str">
+        <x:v>겹친 동굴과 절벽 안쪽 길. 천장이 포물선 공격을 막습니다.</x:v>
+      </x:c>
+      <x:c r="C207" s="45" t="str">
+        <x:v>Layered cave routes whose ceilings block overhead shots.</x:v>
+      </x:c>
+      <x:c r="D207" s="45" t="str">
+        <x:v>맵과 탈출 도구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="58" customHeight="1">
+      <x:c r="A208" s="45" t="str">
+        <x:v>map_sky_terraces</x:v>
+      </x:c>
+      <x:c r="B208" s="45" t="str">
+        <x:v>층층 협곡</x:v>
+      </x:c>
+      <x:c r="C208" s="45" t="str">
+        <x:v>Sky Terraces</x:v>
+      </x:c>
+      <x:c r="D208" s="45" t="str">
+        <x:v>맵과 탈출 도구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="58" customHeight="1">
+      <x:c r="A209" s="45" t="str">
+        <x:v>map_sky_terraces_description</x:v>
+      </x:c>
+      <x:c r="B209" s="45" t="str">
+        <x:v>큰 단차와 겹친 발판. 고지는 넓은 시야와 추락 위험을 함께 줍니다.</x:v>
+      </x:c>
+      <x:c r="C209" s="45" t="str">
+        <x:v>Stepped cliffs and overhangs trade sightlines for fall risk.</x:v>
+      </x:c>
+      <x:c r="D209" s="45" t="str">
+        <x:v>맵과 탈출 도구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="58" customHeight="1">
+      <x:c r="A210" s="45" t="str">
+        <x:v>common_eraser</x:v>
+      </x:c>
+      <x:c r="B210" s="45" t="str">
+        <x:v>지우개</x:v>
+      </x:c>
+      <x:c r="C210" s="45" t="str">
+        <x:v>Eraser</x:v>
+      </x:c>
+      <x:c r="D210" s="45" t="str">
+        <x:v>맵과 탈출 도구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="58" customHeight="1">
+      <x:c r="A211" s="45" t="str">
+        <x:v>common_eraser_description</x:v>
+      </x:c>
+      <x:c r="B211" s="45" t="str">
+        <x:v>주변 지형을 넓게 삭제합니다. 차징할수록 범위 증가. 직접 피해 없음.</x:v>
+      </x:c>
+      <x:c r="C211" s="45" t="str">
+        <x:v>Erase nearby terrain. Charge for a wider radius. No direct damage.</x:v>
+      </x:c>
+      <x:c r="D211" s="45" t="str">
+        <x:v>맵과 탈출 도구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="58" customHeight="1">
+      <x:c r="A212" s="45" t="str">
+        <x:v>common_crystal</x:v>
+      </x:c>
+      <x:c r="B212" s="45" t="str">
+        <x:v>수정구</x:v>
+      </x:c>
+      <x:c r="C212" s="45" t="str">
+        <x:v>Crystal Orb</x:v>
+      </x:c>
+      <x:c r="D212" s="45" t="str">
+        <x:v>탄착점 순간이동</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="58" customHeight="1">
+      <x:c r="A213" s="45" t="str">
+        <x:v>common_crystal_description</x:v>
+      </x:c>
+      <x:c r="B213" s="45" t="str">
+        <x:v>탄착점 근처의 빈 공간으로 순간이동합니다. 막힌 곳에는 이동하지 않습니다.</x:v>
+      </x:c>
+      <x:c r="C213" s="45" t="str">
+        <x:v>Teleport to clear space near impact. Blocked destinations fail.</x:v>
+      </x:c>
+      <x:c r="D213" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="58" customHeight="1">
+      <x:c r="A214" s="45" t="str">
+        <x:v>common_heavy</x:v>
+      </x:c>
+      <x:c r="B214" s="45" t="str">
+        <x:v>중화기</x:v>
+      </x:c>
+      <x:c r="C214" s="45" t="str">
+        <x:v>Heavy Weapon</x:v>
+      </x:c>
+      <x:c r="D214" s="45" t="str">
+        <x:v>헬기 지원</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="58" customHeight="1">
+      <x:c r="A215" s="45" t="str">
+        <x:v>common_heavy_description</x:v>
+      </x:c>
+      <x:c r="B215" s="45" t="str">
+        <x:v>요란한 가짜 폭발 뒤 헬기가 공격합니다. 기관총과 런처의 피해와 범위는 같습니다.</x:v>
+      </x:c>
+      <x:c r="C215" s="45" t="str">
+        <x:v>A fake blast precedes helicopter support. MG and launcher deal identical damage in the same area.</x:v>
+      </x:c>
+      <x:c r="D215" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="58" customHeight="1">
+      <x:c r="A216" s="45" t="str">
+        <x:v>map_low_cavern</x:v>
+      </x:c>
+      <x:c r="B216" s="45" t="str">
+        <x:v>낮은 천장 동굴</x:v>
+      </x:c>
+      <x:c r="C216" s="45" t="str">
+        <x:v>Low Cavern</x:v>
+      </x:c>
+      <x:c r="D216" s="45" t="str">
+        <x:v>신규 맵</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="58" customHeight="1">
+      <x:c r="A217" s="45" t="str">
+        <x:v>map_low_cavern_description</x:v>
+      </x:c>
+      <x:c r="B217" s="45" t="str">
+        <x:v>낮은 바위 천장이 높은 포물선 공격을 막습니다. 동굴 안쪽 길을 활용하세요.</x:v>
+      </x:c>
+      <x:c r="C217" s="45" t="str">
+        <x:v>A low rock ceiling blocks high arcs. Use the sheltered passage.</x:v>
+      </x:c>
+      <x:c r="D217" s="45" t="str">
+        <x:v>신규 맵</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="58" customHeight="1">
+      <x:c r="A218" s="45" t="str">
+        <x:v>vacuum_name</x:v>
+      </x:c>
+      <x:c r="B218" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C218" s="45" t="str">
+        <x:v>Vacuum</x:v>
+      </x:c>
+      <x:c r="D218" s="45" t="str">
+        <x:v>캐릭터</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="58" customHeight="1">
+      <x:c r="A219" s="45" t="str">
+        <x:v>vacuum_description</x:v>
+      </x:c>
+      <x:c r="B219" s="45" t="str">
+        <x:v>직선 바람으로 밀거나 당기고, 공용머리를 회수하며 공중 이동합니다.</x:v>
+      </x:c>
+      <x:c r="C219" s="45" t="str">
+        <x:v>Push or pull with directed airflow, retrieve shared heads, and hover.</x:v>
+      </x:c>
+      <x:c r="D219" s="45" t="str">
+        <x:v>캐릭터</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="58" customHeight="1">
+      <x:c r="A220" s="45" t="str">
+        <x:v>vacuum_skill_1</x:v>
+      </x:c>
+      <x:c r="B220" s="45" t="str">
+        <x:v>강풍 분사</x:v>
+      </x:c>
+      <x:c r="C220" s="45" t="str">
+        <x:v>Gust</x:v>
+      </x:c>
+      <x:c r="D220" s="45" t="str">
+        <x:v>청소기 1번</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="58" customHeight="1">
+      <x:c r="A221" s="45" t="str">
+        <x:v>vacuum_skill_1_description</x:v>
+      </x:c>
+      <x:c r="B221" s="45" t="str">
+        <x:v>조준 방향의 캐릭터를 밀어냅니다. 차징할수록 거리와 힘이 증가합니다.</x:v>
+      </x:c>
+      <x:c r="C221" s="45" t="str">
+        <x:v>Push characters along the aim direction. Charge increases reach and force.</x:v>
+      </x:c>
+      <x:c r="D221" s="45" t="str">
+        <x:v>청소기 1번</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="58" customHeight="1">
+      <x:c r="A222" s="45" t="str">
+        <x:v>vacuum_skill_2</x:v>
+      </x:c>
+      <x:c r="B222" s="45" t="str">
+        <x:v>집중 흡입</x:v>
+      </x:c>
+      <x:c r="C222" s="45" t="str">
+        <x:v>Suction</x:v>
+      </x:c>
+      <x:c r="D222" s="45" t="str">
+        <x:v>청소기 2번</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="58" customHeight="1">
+      <x:c r="A223" s="45" t="str">
+        <x:v>vacuum_skill_2_description</x:v>
+      </x:c>
+      <x:c r="B223" s="45" t="str">
+        <x:v>직선 범위의 캐릭터를 당기고 가까운 공용머리부터 끌어옵니다. 차징으로 거리와 힘이 증가합니다.</x:v>
+      </x:c>
+      <x:c r="C223" s="45" t="str">
+        <x:v>Pull characters and retrieve the nearest shared heads in a straight corridor. Charge increases reach and force.</x:v>
+      </x:c>
+      <x:c r="D223" s="45" t="str">
+        <x:v>청소기 2번</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="58" customHeight="1">
+      <x:c r="A224" s="45" t="str">
+        <x:v>vacuum_skill_3</x:v>
+      </x:c>
+      <x:c r="B224" s="45" t="str">
+        <x:v>에어 리프트</x:v>
+      </x:c>
+      <x:c r="C224" s="45" t="str">
+        <x:v>Air Lift</x:v>
+      </x:c>
+      <x:c r="D224" s="45" t="str">
+        <x:v>청소기 3번</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="58" customHeight="1">
+      <x:c r="A225" s="45" t="str">
+        <x:v>vacuum_skill_3_description</x:v>
+      </x:c>
+      <x:c r="B225" s="45" t="str">
+        <x:v>차징에 비례한 높이로 잠시 떠서 이동합니다. 이동시간이 늘고 착지 시 낙하 피해를 받지 않습니다.</x:v>
+      </x:c>
+      <x:c r="C225" s="45" t="str">
+        <x:v>Hover at a charge-dependent height with extra movement time and protected landing.</x:v>
+      </x:c>
+      <x:c r="D225" s="45" t="str">
+        <x:v>청소기 3번</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="58" customHeight="1">
+      <x:c r="A226" s="45" t="str">
+        <x:v>training_all_heads</x:v>
+      </x:c>
+      <x:c r="B226" s="45" t="str">
+        <x:v>전체 머리 인벤토리</x:v>
+      </x:c>
+      <x:c r="C226" s="45" t="str">
+        <x:v>All Heads</x:v>
+      </x:c>
+      <x:c r="D226" s="45" t="str">
+        <x:v>훈련장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="58" customHeight="1">
+      <x:c r="A227" s="45" t="str">
+        <x:v>inventory_all</x:v>
+      </x:c>
+      <x:c r="B227" s="45" t="str">
+        <x:v>전체</x:v>
+      </x:c>
+      <x:c r="C227" s="45" t="str">
+        <x:v>All</x:v>
+      </x:c>
+      <x:c r="D227" s="45" t="str">
+        <x:v>머리 인벤토리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="58" customHeight="1">
+      <x:c r="A228" s="45" t="str">
+        <x:v>inventory_characters</x:v>
+      </x:c>
+      <x:c r="B228" s="45" t="str">
+        <x:v>캐릭터 스킬</x:v>
+      </x:c>
+      <x:c r="C228" s="45" t="str">
+        <x:v>Character Skills</x:v>
+      </x:c>
+      <x:c r="D228" s="45" t="str">
+        <x:v>머리 인벤토리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="58" customHeight="1">
+      <x:c r="A229" s="45" t="str">
+        <x:v>inventory_common</x:v>
+      </x:c>
+      <x:c r="B229" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+      <x:c r="C229" s="45" t="str">
+        <x:v>Shared Heads</x:v>
+      </x:c>
+      <x:c r="D229" s="45" t="str">
+        <x:v>머리 인벤토리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="58" customHeight="1">
+      <x:c r="A230" s="45" t="str">
+        <x:v>inventory_search</x:v>
+      </x:c>
+      <x:c r="B230" s="45" t="str">
+        <x:v>머리 이름 검색</x:v>
+      </x:c>
+      <x:c r="C230" s="45" t="str">
+        <x:v>Search heads</x:v>
+      </x:c>
+      <x:c r="D230" s="45" t="str">
+        <x:v>머리 인벤토리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="58" customHeight="1">
+      <x:c r="A231" s="45" t="str">
+        <x:v>inventory_training_help</x:v>
+      </x:c>
+      <x:c r="B231" s="45" t="str">
+        <x:v>머리를 선택하고 조준해서 사용하세요. 훈련장에서는 횟수와 쿨타임이 무제한입니다.</x:v>
+      </x:c>
+      <x:c r="C231" s="45" t="str">
+        <x:v>Select a head, aim and use it. Training has unlimited uses and no cooldowns.</x:v>
+      </x:c>
+      <x:c r="D231" s="45" t="str">
+        <x:v>훈련장</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="58" customHeight="1">
+      <x:c r="A232" s="45" t="str">
+        <x:v>common_attack</x:v>
+      </x:c>
+      <x:c r="B232" s="45" t="str">
+        <x:v>폭탄</x:v>
+      </x:c>
+      <x:c r="C232" s="45" t="str">
+        <x:v>Bomb</x:v>
+      </x:c>
+      <x:c r="D232" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="58" customHeight="1">
+      <x:c r="A233" s="45" t="str">
+        <x:v>common_mobility</x:v>
+      </x:c>
+      <x:c r="B233" s="45" t="str">
+        <x:v>날개</x:v>
+      </x:c>
+      <x:c r="C233" s="45" t="str">
+        <x:v>Wings</x:v>
+      </x:c>
+      <x:c r="D233" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="58" customHeight="1">
+      <x:c r="A234" s="45" t="str">
+        <x:v>common_terrain</x:v>
+      </x:c>
+      <x:c r="B234" s="45" t="str">
+        <x:v>구름</x:v>
+      </x:c>
+      <x:c r="C234" s="45" t="str">
+        <x:v>Cloud</x:v>
+      </x:c>
+      <x:c r="D234" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="58" customHeight="1">
+      <x:c r="A235" s="45" t="str">
+        <x:v>gourd_name</x:v>
+      </x:c>
+      <x:c r="B235" s="45" t="str">
+        <x:v>호리병</x:v>
+      </x:c>
+      <x:c r="C235" s="45" t="str">
+        <x:v>Gourd</x:v>
+      </x:c>
+      <x:c r="D235" s="45" t="str">
+        <x:v>캐릭터</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="58" customHeight="1">
+      <x:c r="A236" s="45" t="str">
+        <x:v>gourd_description</x:v>
+      </x:c>
+      <x:c r="B236" s="45" t="str">
+        <x:v>무작위 머리를 꺼내거나 유한한 머리 보관함에서 골라 사용합니다.</x:v>
+      </x:c>
+      <x:c r="C236" s="45" t="str">
+        <x:v>Draw a mystery head or choose from a finite arsenal.</x:v>
+      </x:c>
+      <x:c r="D236" s="45" t="str">
+        <x:v>캐릭터</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="58" customHeight="1">
+      <x:c r="A237" s="45" t="str">
+        <x:v>gourd_skill_1</x:v>
+      </x:c>
+      <x:c r="B237" s="45" t="str">
+        <x:v>깜짝 주머니</x:v>
+      </x:c>
+      <x:c r="C237" s="45" t="str">
+        <x:v>Mystery Draw</x:v>
+      </x:c>
+      <x:c r="D237" s="45" t="str">
+        <x:v>호리병 1번</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="58" customHeight="1">
+      <x:c r="A238" s="45" t="str">
+        <x:v>gourd_skill_1_description</x:v>
+      </x:c>
+      <x:c r="B238" s="45" t="str">
+        <x:v>발사할 때 다른 캐릭터 스킬 또는 공용머리가 무작위로 공개됩니다.</x:v>
+      </x:c>
+      <x:c r="C238" s="45" t="str">
+        <x:v>A random other-character skill or shared head is revealed only when fired.</x:v>
+      </x:c>
+      <x:c r="D238" s="45" t="str">
+        <x:v>호리병</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="58" customHeight="1">
+      <x:c r="A239" s="45" t="str">
+        <x:v>gourd_skill_2</x:v>
+      </x:c>
+      <x:c r="B239" s="45" t="str">
+        <x:v>주머니 채우기</x:v>
+      </x:c>
+      <x:c r="C239" s="45" t="str">
+        <x:v>Refill Arsenal</x:v>
+      </x:c>
+      <x:c r="D239" s="45" t="str">
+        <x:v>호리병 2번</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="58" customHeight="1">
+      <x:c r="A240" s="45" t="str">
+        <x:v>gourd_skill_2_description</x:v>
+      </x:c>
+      <x:c r="B240" s="45" t="str">
+        <x:v>보관함의 모든 머리 사용 횟수를 1회씩 회복합니다.</x:v>
+      </x:c>
+      <x:c r="C240" s="45" t="str">
+        <x:v>Restore one use to every head in the arsenal.</x:v>
+      </x:c>
+      <x:c r="D240" s="45" t="str">
+        <x:v>호리병</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="58" customHeight="1">
+      <x:c r="A241" s="45" t="str">
+        <x:v>gourd_skill_3</x:v>
+      </x:c>
+      <x:c r="B241" s="45" t="str">
+        <x:v>만물 보관함</x:v>
+      </x:c>
+      <x:c r="C241" s="45" t="str">
+        <x:v>Head Arsenal</x:v>
+      </x:c>
+      <x:c r="D241" s="45" t="str">
+        <x:v>호리병 3번</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="58" customHeight="1">
+      <x:c r="A242" s="45" t="str">
+        <x:v>gourd_skill_3_description</x:v>
+      </x:c>
+      <x:c r="B242" s="45" t="str">
+        <x:v>인벤토리에서 머리를 선택합니다. 머리별 초기 1회 사용, 쿨타임 없음.</x:v>
+      </x:c>
+      <x:c r="C242" s="45" t="str">
+        <x:v>Choose a head from the inventory. Each starts with one use and has no cooldown.</x:v>
+      </x:c>
+      <x:c r="D242" s="45" t="str">
+        <x:v>호리병</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="58" customHeight="1">
+      <x:c r="A243" s="45" t="str">
+        <x:v>gourd_inventory</x:v>
+      </x:c>
+      <x:c r="B243" s="45" t="str">
+        <x:v>호리병 보관함</x:v>
+      </x:c>
+      <x:c r="C243" s="45" t="str">
+        <x:v>Gourd Arsenal</x:v>
+      </x:c>
+      <x:c r="D243" s="45" t="str">
+        <x:v>인벤토리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" ht="58" customHeight="1">
+      <x:c r="A244" s="45" t="str">
+        <x:v>gourd_inventory_help</x:v>
+      </x:c>
+      <x:c r="B244" s="45" t="str">
+        <x:v>머리별 1회 사용 · 2번으로 전체 +1회 · 자기 복제 기술은 제외됩니다.</x:v>
+      </x:c>
+      <x:c r="C244" s="45" t="str">
+        <x:v>One use per head. Skill 2 refills all by one. Recursive gourd skills are excluded.</x:v>
+      </x:c>
+      <x:c r="D244" s="45" t="str">
+        <x:v>인벤토리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" ht="58" customHeight="1">
+      <x:c r="A245" s="45" t="str">
+        <x:v>common_tv</x:v>
+      </x:c>
+      <x:c r="B245" s="45" t="str">
+        <x:v>레트로 TV</x:v>
+      </x:c>
+      <x:c r="C245" s="45" t="str">
+        <x:v>Retro TV</x:v>
+      </x:c>
+      <x:c r="D245" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" ht="58" customHeight="1">
+      <x:c r="A246" s="45" t="str">
+        <x:v>common_tv_description</x:v>
+      </x:c>
+      <x:c r="B246" s="45" t="str">
+        <x:v>탄착 높이를 따라 냥캣이 왼쪽에서 오른쪽으로 지나가며 지형을 파괴하고 모두에게 피해를 줍니다.</x:v>
+      </x:c>
+      <x:c r="C246" s="45" t="str">
+        <x:v>A rainbow cat sweeps left to right at impact height, destroying terrain and damaging both sides.</x:v>
+      </x:c>
+      <x:c r="D246" s="45" t="str">
+        <x:v>공용머리</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3019,7 +3985,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ffd7d9c488b40d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75bd82943b3249cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3127,7 +4093,7 @@
         <x:v>턴</x:v>
       </x:c>
       <x:c r="C7" s="34" t="n">
-        <x:v>1</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="D7" s="25" t="str">
         <x:v>초</x:v>
@@ -5600,16 +6566,16 @@
         <x:v>skill.revolver.3.radius</x:v>
       </x:c>
       <x:c r="B131" s="44" t="str">
-        <x:v>추가 캐릭터</x:v>
+        <x:v>리볼버 3번</x:v>
       </x:c>
       <x:c r="C131" s="44" t="n">
-        <x:v>1.35</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="D131" s="44" t="str">
         <x:v>월드 단위</x:v>
       </x:c>
       <x:c r="E131" s="44" t="str">
-        <x:v>효과 반경</x:v>
+        <x:v>공습 폭발 반경. 아군과 적군 모두 피해</x:v>
       </x:c>
       <x:c r="F131" s="44" t="str">
         <x:v>연결</x:v>
@@ -5643,7 +6609,7 @@
         <x:v>추가 캐릭터</x:v>
       </x:c>
       <x:c r="C133" s="44" t="n">
-        <x:v>1.1</x:v>
+        <x:v>2.2</x:v>
       </x:c>
       <x:c r="D133" s="44" t="str">
         <x:v>월드 단위</x:v>
@@ -5703,7 +6669,7 @@
         <x:v>추가 캐릭터</x:v>
       </x:c>
       <x:c r="C136" s="44" t="n">
-        <x:v>24</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D136" s="44" t="str">
         <x:v>px</x:v>
@@ -6472,6 +7438,866 @@
         <x:v>훈련장 행동 시간</x:v>
       </x:c>
       <x:c r="F174" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="48" customHeight="1">
+      <x:c r="A175" s="46" t="str">
+        <x:v>common.lock.radius</x:v>
+      </x:c>
+      <x:c r="B175" s="46" t="str">
+        <x:v>자물쇠</x:v>
+      </x:c>
+      <x:c r="C175" s="46" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="D175" s="46" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E175" s="46" t="str">
+        <x:v>아군·적군 모두 포획하는 반경</x:v>
+      </x:c>
+      <x:c r="F175" s="46" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="48" customHeight="1">
+      <x:c r="A176" s="46" t="str">
+        <x:v>common.lock.turns</x:v>
+      </x:c>
+      <x:c r="B176" s="46" t="str">
+        <x:v>자물쇠</x:v>
+      </x:c>
+      <x:c r="C176" s="46" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D176" s="46" t="str">
+        <x:v>라운드</x:v>
+      </x:c>
+      <x:c r="E176" s="46" t="str">
+        <x:v>1~2라운드. 해당 캐릭터의 다음 차례를 건너뛰고 봉인 피해 적용</x:v>
+      </x:c>
+      <x:c r="F176" s="46" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="48" customHeight="1">
+      <x:c r="A177" s="46" t="str">
+        <x:v>common.lock.tick_damage</x:v>
+      </x:c>
+      <x:c r="B177" s="46" t="str">
+        <x:v>자물쇠</x:v>
+      </x:c>
+      <x:c r="C177" s="46" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D177" s="46" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E177" s="46" t="str">
+        <x:v>포획 라운드마다 봉인 피해. 헬멧 보호막은 소비하지 않음</x:v>
+      </x:c>
+      <x:c r="F177" s="46" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="48" customHeight="1">
+      <x:c r="A178" s="46" t="str">
+        <x:v>ai.beginner.decision_delay</x:v>
+      </x:c>
+      <x:c r="B178" s="46" t="str">
+        <x:v>AI 초보</x:v>
+      </x:c>
+      <x:c r="C178" s="46" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="D178" s="46" t="str">
+        <x:v>초</x:v>
+      </x:c>
+      <x:c r="E178" s="46" t="str">
+        <x:v>판단 전 대기 시간</x:v>
+      </x:c>
+      <x:c r="F178" s="46" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="48" customHeight="1">
+      <x:c r="A179" s="46" t="str">
+        <x:v>ai.beginner.aim_error_degrees</x:v>
+      </x:c>
+      <x:c r="B179" s="46" t="str">
+        <x:v>AI 초보</x:v>
+      </x:c>
+      <x:c r="C179" s="46" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D179" s="46" t="str">
+        <x:v>도</x:v>
+      </x:c>
+      <x:c r="E179" s="46" t="str">
+        <x:v>최대 조준 오차</x:v>
+      </x:c>
+      <x:c r="F179" s="46" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="48" customHeight="1">
+      <x:c r="A180" s="46" t="str">
+        <x:v>ai.beginner.power_error</x:v>
+      </x:c>
+      <x:c r="B180" s="46" t="str">
+        <x:v>AI 초보</x:v>
+      </x:c>
+      <x:c r="C180" s="46" t="n">
+        <x:v>0.14</x:v>
+      </x:c>
+      <x:c r="D180" s="46" t="str">
+        <x:v>비율</x:v>
+      </x:c>
+      <x:c r="E180" s="46" t="str">
+        <x:v>최대 투척 세기 오차</x:v>
+      </x:c>
+      <x:c r="F180" s="46" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="48" customHeight="1">
+      <x:c r="A181" s="46" t="str">
+        <x:v>ai.normal.decision_delay</x:v>
+      </x:c>
+      <x:c r="B181" s="46" t="str">
+        <x:v>AI 일반</x:v>
+      </x:c>
+      <x:c r="C181" s="46" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="D181" s="46" t="str">
+        <x:v>초</x:v>
+      </x:c>
+      <x:c r="E181" s="46" t="str">
+        <x:v>판단 전 대기 시간</x:v>
+      </x:c>
+      <x:c r="F181" s="46" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="48" customHeight="1">
+      <x:c r="A182" s="46" t="str">
+        <x:v>ai.normal.aim_error_degrees</x:v>
+      </x:c>
+      <x:c r="B182" s="46" t="str">
+        <x:v>AI 일반</x:v>
+      </x:c>
+      <x:c r="C182" s="46" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D182" s="46" t="str">
+        <x:v>도</x:v>
+      </x:c>
+      <x:c r="E182" s="46" t="str">
+        <x:v>최대 조준 오차</x:v>
+      </x:c>
+      <x:c r="F182" s="46" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="48" customHeight="1">
+      <x:c r="A183" s="46" t="str">
+        <x:v>ai.normal.power_error</x:v>
+      </x:c>
+      <x:c r="B183" s="46" t="str">
+        <x:v>AI 일반</x:v>
+      </x:c>
+      <x:c r="C183" s="46" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="D183" s="46" t="str">
+        <x:v>비율</x:v>
+      </x:c>
+      <x:c r="E183" s="46" t="str">
+        <x:v>최대 투척 세기 오차</x:v>
+      </x:c>
+      <x:c r="F183" s="46" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="48" customHeight="1">
+      <x:c r="A184" s="46" t="str">
+        <x:v>ai.pro.decision_delay</x:v>
+      </x:c>
+      <x:c r="B184" s="46" t="str">
+        <x:v>AI 프로</x:v>
+      </x:c>
+      <x:c r="C184" s="46" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="D184" s="46" t="str">
+        <x:v>초</x:v>
+      </x:c>
+      <x:c r="E184" s="46" t="str">
+        <x:v>판단 전 대기 시간</x:v>
+      </x:c>
+      <x:c r="F184" s="46" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="48" customHeight="1">
+      <x:c r="A185" s="46" t="str">
+        <x:v>ai.pro.aim_error_degrees</x:v>
+      </x:c>
+      <x:c r="B185" s="46" t="str">
+        <x:v>AI 프로</x:v>
+      </x:c>
+      <x:c r="C185" s="46" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="D185" s="46" t="str">
+        <x:v>도</x:v>
+      </x:c>
+      <x:c r="E185" s="46" t="str">
+        <x:v>최대 조준 오차</x:v>
+      </x:c>
+      <x:c r="F185" s="46" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="48" customHeight="1">
+      <x:c r="A186" s="46" t="str">
+        <x:v>ai.pro.power_error</x:v>
+      </x:c>
+      <x:c r="B186" s="46" t="str">
+        <x:v>AI 프로</x:v>
+      </x:c>
+      <x:c r="C186" s="46" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="D186" s="46" t="str">
+        <x:v>비율</x:v>
+      </x:c>
+      <x:c r="E186" s="46" t="str">
+        <x:v>최대 투척 세기 오차</x:v>
+      </x:c>
+      <x:c r="F186" s="46" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="30" customHeight="1">
+      <x:c r="A187" s="44" t="str">
+        <x:v>common.eraser.min_radius</x:v>
+      </x:c>
+      <x:c r="B187" s="44" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+      <x:c r="C187" s="44" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="D187" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E187" s="44" t="str">
+        <x:v>지우개 최소 지형 삭제 반경</x:v>
+      </x:c>
+      <x:c r="F187" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="30" customHeight="1">
+      <x:c r="A188" s="44" t="str">
+        <x:v>common.eraser.max_radius</x:v>
+      </x:c>
+      <x:c r="B188" s="44" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+      <x:c r="C188" s="44" t="n">
+        <x:v>4.8</x:v>
+      </x:c>
+      <x:c r="D188" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E188" s="44" t="str">
+        <x:v>완전 차징 지형 삭제 반경</x:v>
+      </x:c>
+      <x:c r="F188" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="30" customHeight="1">
+      <x:c r="A189" s="44" t="str">
+        <x:v>common.eraser.clearance</x:v>
+      </x:c>
+      <x:c r="B189" s="44" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+      <x:c r="C189" s="44" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="D189" s="44" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E189" s="44" t="str">
+        <x:v>캐릭터 충돌체 주변 여유</x:v>
+      </x:c>
+      <x:c r="F189" s="44" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="30" customHeight="1">
+      <x:c r="A190" s="45" t="str">
+        <x:v>common.crystal.max_damage</x:v>
+      </x:c>
+      <x:c r="B190" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+      <x:c r="C190" s="45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D190" s="45" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E190" s="45" t="str">
+        <x:v>수정구 직접 피해 없음</x:v>
+      </x:c>
+      <x:c r="F190" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="30" customHeight="1">
+      <x:c r="A191" s="45" t="str">
+        <x:v>common.heavy.max_damage</x:v>
+      </x:c>
+      <x:c r="B191" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+      <x:c r="C191" s="45" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D191" s="45" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E191" s="45" t="str">
+        <x:v>중화기 마지막 공격 최대 피해 (두 연출 공통)</x:v>
+      </x:c>
+      <x:c r="F191" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="30" customHeight="1">
+      <x:c r="A192" s="45" t="str">
+        <x:v>common.heavy.radius</x:v>
+      </x:c>
+      <x:c r="B192" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+      <x:c r="C192" s="45" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D192" s="45" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E192" s="45" t="str">
+        <x:v>중화기 마지막 공격 반경 (두 연출 공통)</x:v>
+      </x:c>
+      <x:c r="F192" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="30" customHeight="1">
+      <x:c r="A193" s="45" t="str">
+        <x:v>common.heavy.terrain_radius_px</x:v>
+      </x:c>
+      <x:c r="B193" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+      <x:c r="C193" s="45" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D193" s="45" t="str">
+        <x:v>픽셀</x:v>
+      </x:c>
+      <x:c r="E193" s="45" t="str">
+        <x:v>중화기 마지막 공격 지형 파괴 반경</x:v>
+      </x:c>
+      <x:c r="F193" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="30" customHeight="1">
+      <x:c r="A194" s="45" t="str">
+        <x:v>common.heavy.force</x:v>
+      </x:c>
+      <x:c r="B194" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+      <x:c r="C194" s="45" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D194" s="45" t="str">
+        <x:v>힘</x:v>
+      </x:c>
+      <x:c r="E194" s="45" t="str">
+        <x:v>중화기 마지막 공격 넉백</x:v>
+      </x:c>
+      <x:c r="F194" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="30" customHeight="1">
+      <x:c r="A195" s="45" t="str">
+        <x:v>vacuum.range_min</x:v>
+      </x:c>
+      <x:c r="B195" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C195" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D195" s="45" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E195" s="45" t="str">
+        <x:v>최소 차징 사거리</x:v>
+      </x:c>
+      <x:c r="F195" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="30" customHeight="1">
+      <x:c r="A196" s="45" t="str">
+        <x:v>vacuum.range_max</x:v>
+      </x:c>
+      <x:c r="B196" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C196" s="45" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D196" s="45" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E196" s="45" t="str">
+        <x:v>최대 차징 사거리</x:v>
+      </x:c>
+      <x:c r="F196" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="30" customHeight="1">
+      <x:c r="A197" s="45" t="str">
+        <x:v>vacuum.force_min</x:v>
+      </x:c>
+      <x:c r="B197" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C197" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D197" s="45" t="str">
+        <x:v>힘</x:v>
+      </x:c>
+      <x:c r="E197" s="45" t="str">
+        <x:v>최소 차징 밀기/당기기 힘</x:v>
+      </x:c>
+      <x:c r="F197" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="30" customHeight="1">
+      <x:c r="A198" s="45" t="str">
+        <x:v>vacuum.force_max</x:v>
+      </x:c>
+      <x:c r="B198" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C198" s="45" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D198" s="45" t="str">
+        <x:v>힘</x:v>
+      </x:c>
+      <x:c r="E198" s="45" t="str">
+        <x:v>최대 차징 밀기/당기기 힘</x:v>
+      </x:c>
+      <x:c r="F198" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="30" customHeight="1">
+      <x:c r="A199" s="45" t="str">
+        <x:v>vacuum.beam_width</x:v>
+      </x:c>
+      <x:c r="B199" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C199" s="45" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="D199" s="45" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E199" s="45" t="str">
+        <x:v>직선 판정 폭</x:v>
+      </x:c>
+      <x:c r="F199" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="30" customHeight="1">
+      <x:c r="A200" s="45" t="str">
+        <x:v>vacuum.maximum_loot</x:v>
+      </x:c>
+      <x:c r="B200" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C200" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D200" s="45" t="str">
+        <x:v>개</x:v>
+      </x:c>
+      <x:c r="E200" s="45" t="str">
+        <x:v>가까운 순 공용머리 흡입 상한</x:v>
+      </x:c>
+      <x:c r="F200" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="30" customHeight="1">
+      <x:c r="A201" s="45" t="str">
+        <x:v>vacuum.loot_seconds</x:v>
+      </x:c>
+      <x:c r="B201" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C201" s="45" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="D201" s="45" t="str">
+        <x:v>초</x:v>
+      </x:c>
+      <x:c r="E201" s="45" t="str">
+        <x:v>공용머리 흡입 시간</x:v>
+      </x:c>
+      <x:c r="F201" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="30" customHeight="1">
+      <x:c r="A202" s="45" t="str">
+        <x:v>vacuum.loot_speed</x:v>
+      </x:c>
+      <x:c r="B202" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C202" s="45" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D202" s="45" t="str">
+        <x:v>월드 단위/초</x:v>
+      </x:c>
+      <x:c r="E202" s="45" t="str">
+        <x:v>공용머리 최대 흡입 속도</x:v>
+      </x:c>
+      <x:c r="F202" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="30" customHeight="1">
+      <x:c r="A203" s="45" t="str">
+        <x:v>vacuum.hover_min</x:v>
+      </x:c>
+      <x:c r="B203" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C203" s="45" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="D203" s="45" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E203" s="45" t="str">
+        <x:v>최소 체공 높이</x:v>
+      </x:c>
+      <x:c r="F203" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="30" customHeight="1">
+      <x:c r="A204" s="45" t="str">
+        <x:v>vacuum.hover_max</x:v>
+      </x:c>
+      <x:c r="B204" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C204" s="45" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D204" s="45" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E204" s="45" t="str">
+        <x:v>최대 체공 높이</x:v>
+      </x:c>
+      <x:c r="F204" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="30" customHeight="1">
+      <x:c r="A205" s="45" t="str">
+        <x:v>vacuum.hover_seconds</x:v>
+      </x:c>
+      <x:c r="B205" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C205" s="45" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D205" s="45" t="str">
+        <x:v>초</x:v>
+      </x:c>
+      <x:c r="E205" s="45" t="str">
+        <x:v>체공 시간</x:v>
+      </x:c>
+      <x:c r="F205" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="30" customHeight="1">
+      <x:c r="A206" s="45" t="str">
+        <x:v>vacuum.extra_movement</x:v>
+      </x:c>
+      <x:c r="B206" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C206" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D206" s="45" t="str">
+        <x:v>초</x:v>
+      </x:c>
+      <x:c r="E206" s="45" t="str">
+        <x:v>추가 이동시간</x:v>
+      </x:c>
+      <x:c r="F206" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="30" customHeight="1">
+      <x:c r="A207" s="45" t="str">
+        <x:v>skill.vacuum.1.cooldown</x:v>
+      </x:c>
+      <x:c r="B207" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C207" s="45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D207" s="45" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E207" s="45" t="str">
+        <x:v>강풍 분사 재사용 대기</x:v>
+      </x:c>
+      <x:c r="F207" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="30" customHeight="1">
+      <x:c r="A208" s="45" t="str">
+        <x:v>skill.vacuum.2.cooldown</x:v>
+      </x:c>
+      <x:c r="B208" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C208" s="45" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D208" s="45" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E208" s="45" t="str">
+        <x:v>집중 흡입 재사용 대기</x:v>
+      </x:c>
+      <x:c r="F208" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="30" customHeight="1">
+      <x:c r="A209" s="45" t="str">
+        <x:v>skill.vacuum.3.cooldown</x:v>
+      </x:c>
+      <x:c r="B209" s="45" t="str">
+        <x:v>청소기</x:v>
+      </x:c>
+      <x:c r="C209" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D209" s="45" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E209" s="45" t="str">
+        <x:v>에어 리프트 재사용 대기</x:v>
+      </x:c>
+      <x:c r="F209" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="30" customHeight="1">
+      <x:c r="A210" s="45" t="str">
+        <x:v>skill.gourd.1.cooldown</x:v>
+      </x:c>
+      <x:c r="B210" s="45" t="str">
+        <x:v>호리병</x:v>
+      </x:c>
+      <x:c r="C210" s="45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D210" s="45" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E210" s="45" t="str">
+        <x:v>무작위 머리 쿨타임</x:v>
+      </x:c>
+      <x:c r="F210" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="30" customHeight="1">
+      <x:c r="A211" s="45" t="str">
+        <x:v>skill.gourd.2.cooldown</x:v>
+      </x:c>
+      <x:c r="B211" s="45" t="str">
+        <x:v>호리병</x:v>
+      </x:c>
+      <x:c r="C211" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D211" s="45" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E211" s="45" t="str">
+        <x:v>전체 재충전 긴 쿨타임</x:v>
+      </x:c>
+      <x:c r="F211" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="30" customHeight="1">
+      <x:c r="A212" s="45" t="str">
+        <x:v>skill.gourd.3.cooldown</x:v>
+      </x:c>
+      <x:c r="B212" s="45" t="str">
+        <x:v>호리병</x:v>
+      </x:c>
+      <x:c r="C212" s="45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D212" s="45" t="str">
+        <x:v>자기 턴</x:v>
+      </x:c>
+      <x:c r="E212" s="45" t="str">
+        <x:v>보관함은 횟수제</x:v>
+      </x:c>
+      <x:c r="F212" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="30" customHeight="1">
+      <x:c r="A213" s="45" t="str">
+        <x:v>character.gourd.hp</x:v>
+      </x:c>
+      <x:c r="B213" s="45" t="str">
+        <x:v>호리병</x:v>
+      </x:c>
+      <x:c r="C213" s="45" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D213" s="45" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E213" s="45" t="str">
+        <x:v>기본 체력</x:v>
+      </x:c>
+      <x:c r="F213" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="30" customHeight="1">
+      <x:c r="A214" s="45" t="str">
+        <x:v>common.tv.max_damage</x:v>
+      </x:c>
+      <x:c r="B214" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+      <x:c r="C214" s="45" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D214" s="45" t="str">
+        <x:v>HP</x:v>
+      </x:c>
+      <x:c r="E214" s="45" t="str">
+        <x:v>수평 경로 내 캐릭터당 1회 피해</x:v>
+      </x:c>
+      <x:c r="F214" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="30" customHeight="1">
+      <x:c r="A215" s="45" t="str">
+        <x:v>common.tv.radius</x:v>
+      </x:c>
+      <x:c r="B215" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+      <x:c r="C215" s="45" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="D215" s="45" t="str">
+        <x:v>월드 단위</x:v>
+      </x:c>
+      <x:c r="E215" s="45" t="str">
+        <x:v>수평 공격 반폭</x:v>
+      </x:c>
+      <x:c r="F215" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="30" customHeight="1">
+      <x:c r="A216" s="45" t="str">
+        <x:v>common.tv.terrain_radius_px</x:v>
+      </x:c>
+      <x:c r="B216" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+      <x:c r="C216" s="45" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D216" s="45" t="str">
+        <x:v>픽셀</x:v>
+      </x:c>
+      <x:c r="E216" s="45" t="str">
+        <x:v>수평 지형 파괴 반경</x:v>
+      </x:c>
+      <x:c r="F216" s="45" t="str">
+        <x:v>연결</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="30" customHeight="1">
+      <x:c r="A217" s="45" t="str">
+        <x:v>common.tv.force</x:v>
+      </x:c>
+      <x:c r="B217" s="45" t="str">
+        <x:v>공용머리</x:v>
+      </x:c>
+      <x:c r="C217" s="45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D217" s="45" t="str">
+        <x:v>힘</x:v>
+      </x:c>
+      <x:c r="E217" s="45" t="str">
+        <x:v>수평 넉백</x:v>
+      </x:c>
+      <x:c r="F217" s="45" t="str">
         <x:v>연결</x:v>
       </x:c>
     </x:row>
@@ -6482,7 +8308,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57617daa4663401e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R617e4c70379d4f88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
